--- a/proforma/246 South 2nd - Base Proforma.xlsx
+++ b/proforma/246 South 2nd - Base Proforma.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jorda\Claude\Projects\246\proforma\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E8421AE2-6C7D-4D40-B92D-F44792EB0B41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{02460463-5D3C-4E2B-80B7-D517521F0691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,12 +33,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1147" uniqueCount="712">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="714">
   <si>
     <t>246 South 2nd Street · Master Pro Forma</t>
   </si>
   <si>
-    <t>246 South 2nd Street on its own 3,100 sf lot in R6 with a commercial overlay: 8 stories at 85 ft (13'-11" ground floor, 11 ft 2nd floor, 10 ft above), plus a cellar and a private roof. 9 condos (8 market-rate and one affordable homeownership unit), 6,879 sellable sf; commercial on the 1st and 2nd floors (4,333 sf sellable) plus 1,857 sf in the cellar; Zone Green (ULEB) 5% exclusion; no air rights or certificates; all-electric. Residential priced at $1,450/sf (base, placeholder until comps).</t>
+    <t>246 South 2nd Street on its own 3,100 sf lot in R6 with a commercial overlay: 8 stories at 85 ft (13'-11" ground floor, 11 ft 2nd floor, 10 ft above), plus a cellar and a private roof. 9 condos (8 market-rate and one affordable homeownership unit), 6,879 sellable sf; commercial on the 1st and 2nd floors (4,333 sf sellable) plus 1,857 sf in the cellar; Zone Green (ULEB) 5% exclusion; no air rights or certificates; all-electric. Residential at $1,750/sf on the 4th floor (base) plus 2% a floor above it.</t>
   </si>
   <si>
     <t>Every figure here is pulled from the Finance, Hard Costs and Soft Costs sheets (green). Change inputs on those sheets, not here.</t>
@@ -320,25 +320,31 @@
     <t>PRICING</t>
   </si>
   <si>
-    <t>Price, standard units</t>
+    <t>Price, standard units (4th floor)</t>
   </si>
   <si>
     <t>$ / sf</t>
   </si>
   <si>
-    <t>Placeholder at 725 Grand's base case, $1,450/sf, until the Southside comps are pulled. The OM compares an upside at $1,650/sf.</t>
-  </si>
-  <si>
-    <t>Mezzanine duplex premium (not used)</t>
-  </si>
-  <si>
-    <t>over standard</t>
-  </si>
-  <si>
-    <t>No duplex or mezzanine units in this design.</t>
-  </si>
-  <si>
-    <t>Price, mezzanine duplexes</t>
+    <t>Owner, Oct 18 2026: base case $1,750/sf on the 4th floor (raised from $1,650); the OM compares an upside at $1,950/sf. Comps to confirm.</t>
+  </si>
+  <si>
+    <t>Premium per floor above the base floor</t>
+  </si>
+  <si>
+    <t>per floor</t>
+  </si>
+  <si>
+    <t>Owner, Oct 18 2026: upper floors carry a premium. 2% a floor: 5th +2%, 6th +4%, 7th +6%, PH (8th) +8%. Feeds column K below.</t>
+  </si>
+  <si>
+    <t>Base floor (no premium)</t>
+  </si>
+  <si>
+    <t>floor</t>
+  </si>
+  <si>
+    <t>The lowest residential floor.</t>
   </si>
   <si>
     <t>SELLABLE-AREA ADJUSTMENT (revenue only)</t>
@@ -401,7 +407,7 @@
     <t>Base $ / sf</t>
   </si>
   <si>
-    <t>Unit premium / discount</t>
+    <t>Floor premium</t>
   </si>
   <si>
     <t>Asking price override ($)</t>
@@ -2323,7 +2329,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2414,6 +2420,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="174" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -2953,11 +2962,11 @@
       </c>
       <c r="B19" s="26">
         <f>'Rev &amp; Unit-by-Unit'!$M$27</f>
-        <v>9030450</v>
+        <v>11258605</v>
       </c>
       <c r="C19" s="9">
         <f>B19/$B$7</f>
-        <v>1312.7562145660706</v>
+        <v>1636.6630324175026</v>
       </c>
       <c r="E19" s="19" t="s">
         <v>26</v>
@@ -2969,7 +2978,7 @@
       </c>
       <c r="B20" s="26">
         <f>'Rev &amp; Unit-by-Unit'!$N$27</f>
-        <v>1312.7562145660706</v>
+        <v>1636.6630324175026</v>
       </c>
       <c r="E20" s="19" t="s">
         <v>28</v>
@@ -2981,7 +2990,7 @@
       </c>
       <c r="B21" s="26">
         <f>'Rev &amp; Unit-by-Unit'!$G$6</f>
-        <v>1450</v>
+        <v>1750</v>
       </c>
       <c r="E21" s="19" t="s">
         <v>30</v>
@@ -3009,11 +3018,11 @@
       </c>
       <c r="B23" s="13">
         <f>B19+B22</f>
-        <v>14126248</v>
+        <v>16354403</v>
       </c>
       <c r="C23" s="13">
         <f>B23/$B$7</f>
-        <v>2053.5321994475939</v>
+        <v>2377.4390172990261</v>
       </c>
       <c r="D23" s="14"/>
       <c r="E23" s="14"/>
@@ -3024,11 +3033,11 @@
       </c>
       <c r="B24" s="26">
         <f>-'Rev &amp; Unit-by-Unit'!$M$61</f>
-        <v>-518219.21249999997</v>
+        <v>-625727.69125000003</v>
       </c>
       <c r="C24" s="9">
         <f>B24/$B$7</f>
-        <v>-75.333509594417791</v>
+        <v>-90.962013555749394</v>
       </c>
       <c r="E24" s="19" t="s">
         <v>35</v>
@@ -3066,11 +3075,11 @@
       </c>
       <c r="B27" s="13">
         <f>'Rev &amp; Unit-by-Unit'!$M$78</f>
-        <v>13075914.533</v>
+        <v>15196561.05425</v>
       </c>
       <c r="C27" s="13">
         <f>B27/$B$7</f>
-        <v>1900.8452584678005</v>
+        <v>2209.1235723579007</v>
       </c>
       <c r="D27" s="14"/>
       <c r="E27" s="14"/>
@@ -3292,11 +3301,11 @@
       </c>
       <c r="B43" s="13">
         <f>B27-B40</f>
-        <v>-22611.515407018363</v>
+        <v>2098035.0058429819</v>
       </c>
       <c r="C43" s="13">
         <f>B43/$B$7</f>
-        <v>-3.2870352387001547</v>
+        <v>304.99127865140019</v>
       </c>
       <c r="D43" s="14"/>
       <c r="E43" s="14"/>
@@ -3307,7 +3316,7 @@
       </c>
       <c r="B44" s="11">
         <f>B43/B40</f>
-        <v>-1.7262641096757808E-3</v>
+        <v>0.16017336592601847</v>
       </c>
       <c r="E44" s="19" t="s">
         <v>58</v>
@@ -3319,7 +3328,7 @@
       </c>
       <c r="B45" s="9">
         <f>B43/B6</f>
-        <v>-2512.3906007798182</v>
+        <v>233115.00064922019</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -3328,7 +3337,7 @@
       </c>
       <c r="B46" s="9">
         <f>Finance!$B$52-B43</f>
-        <v>2.7939677238464355E-9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -3361,7 +3370,7 @@
       </c>
       <c r="B49" s="13">
         <f>B43-B47-B48</f>
-        <v>-259605.52290701837</v>
+        <v>1861040.9983429818</v>
       </c>
       <c r="C49" s="14"/>
       <c r="D49" s="14"/>
@@ -3375,7 +3384,7 @@
       </c>
       <c r="B50" s="11">
         <f>B49/B40</f>
-        <v>-1.9819445481699095E-2</v>
+        <v>0.14208018455399513</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="13" x14ac:dyDescent="0.3">
@@ -3424,7 +3433,7 @@
       </c>
       <c r="B58" s="27">
         <f>Finance!$B$54</f>
-        <v>0.99486291396289328</v>
+        <v>1.4766503323582276</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
@@ -3433,7 +3442,7 @@
       </c>
       <c r="B59" s="31">
         <f>Finance!$B$55</f>
-        <v>-5.1370860371067403E-3</v>
+        <v>0.47665033235822762</v>
       </c>
       <c r="E59" s="19" t="s">
         <v>76</v>
@@ -3445,7 +3454,7 @@
       </c>
       <c r="B60" s="31">
         <f>Finance!$B$56</f>
-        <v>-2.3193882013247125E-3</v>
+        <v>0.19175426332777623</v>
       </c>
       <c r="E60" s="19" t="s">
         <v>78</v>
@@ -3457,7 +3466,7 @@
       </c>
       <c r="B61" s="31">
         <f>Finance!$B$57</f>
-        <v>5.9801144244321813E-2</v>
+        <v>0.18673943747403277</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -3466,7 +3475,7 @@
       </c>
       <c r="B62" s="31">
         <f>Finance!$B$60</f>
-        <v>-2.3193882013247125E-3</v>
+        <v>0.15722847952732177</v>
       </c>
       <c r="E62" s="19" t="s">
         <v>81</v>
@@ -3478,7 +3487,7 @@
       </c>
       <c r="B63" s="27">
         <f>Finance!$B$59</f>
-        <v>0.99486291396289306</v>
+        <v>1.3831669424436841</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -3487,7 +3496,7 @@
       </c>
       <c r="B64" s="26">
         <f>Finance!$B$61</f>
-        <v>0</v>
+        <v>411478.62739383924</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
@@ -3496,7 +3505,7 @@
       </c>
       <c r="B65" s="31">
         <f>Finance!$B$63</f>
-        <v>-2.3193882013247125E-3</v>
+        <v>0.45915342500232237</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="13" x14ac:dyDescent="0.3">
@@ -3585,7 +3594,7 @@
         <v>95</v>
       </c>
       <c r="G6" s="7">
-        <v>1450</v>
+        <v>1750</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>96</v>
@@ -3599,7 +3608,7 @@
         <v>98</v>
       </c>
       <c r="G7" s="8">
-        <v>0.2</v>
+        <v>0.02</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>99</v>
@@ -3612,66 +3621,68 @@
       <c r="A8" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="G8" s="9">
-        <f>$G$6*(1+$G$7)</f>
-        <v>1740</v>
+      <c r="G8" s="40">
+        <v>4</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>96</v>
+        <v>102</v>
+      </c>
+      <c r="I8" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A10" s="18" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="25" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G11" s="28">
         <f>'Hard Costs'!$C$10</f>
         <v>6879</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="G12" s="32">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="G12" s="32">
-        <v>0</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>104</v>
-      </c>
       <c r="I12" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G13" s="33">
         <f>IF($G$12&gt;0,$G$12-$G$11,0)</f>
         <v>0</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="25" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G14" s="34">
         <f>$G$13/$G$11</f>
@@ -3681,54 +3692,54 @@
     </row>
     <row r="16" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A16" s="18" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="17" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="P17" s="3" t="s">
         <v>24</v>
@@ -3736,10 +3747,10 @@
     </row>
     <row r="18" spans="1:16" ht="24" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C18" s="28" t="str">
         <f>'Hard Costs'!$B$29</f>
@@ -3756,7 +3767,7 @@
         <f>IF('Hard Costs'!$H$29=1,"Yes","No")</f>
         <v>No</v>
       </c>
-      <c r="G18" s="40">
+      <c r="G18" s="41">
         <v>858</v>
       </c>
       <c r="H18" s="33">
@@ -3768,36 +3779,37 @@
         <v>858</v>
       </c>
       <c r="J18" s="9">
-        <f>IF('Hard Costs'!$H$29=1,$G$8,$G$6)</f>
-        <v>1450</v>
+        <f t="shared" ref="J18:J26" si="2">$G$6</f>
+        <v>1750</v>
       </c>
       <c r="K18" s="8">
-        <v>0</v>
-      </c>
-      <c r="L18" s="41">
+        <f t="shared" ref="K18:K26" si="3">MAX(0,VALUE(B18)-$G$8)*$G$7</f>
+        <v>0</v>
+      </c>
+      <c r="L18" s="42">
         <v>300000</v>
       </c>
       <c r="M18" s="9">
-        <f t="shared" ref="M18:M26" si="2">IF(N(L18)&gt;0,L18,I18*J18*(1+K18))</f>
+        <f t="shared" ref="M18:M26" si="4">IF(N(L18)&gt;0,L18,I18*J18*(1+K18))</f>
         <v>300000</v>
       </c>
       <c r="N18" s="9">
-        <f t="shared" ref="N18:N27" si="3">M18/I18</f>
+        <f t="shared" ref="N18:N27" si="5">M18/I18</f>
         <v>349.65034965034965</v>
       </c>
       <c r="O18" s="6">
         <v>1</v>
       </c>
       <c r="P18" s="19" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="19" spans="1:16" ht="13" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="B19" s="4" t="s">
         <v>130</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>128</v>
       </c>
       <c r="C19" s="28" t="str">
         <f>'Hard Costs'!$B$30</f>
@@ -3814,7 +3826,7 @@
         <f>IF('Hard Costs'!$H$30=1,"Yes","No")</f>
         <v>No</v>
       </c>
-      <c r="G19" s="40">
+      <c r="G19" s="41">
         <v>714</v>
       </c>
       <c r="H19" s="33">
@@ -3826,34 +3838,35 @@
         <v>714</v>
       </c>
       <c r="J19" s="9">
-        <f>IF('Hard Costs'!$H$30=1,$G$8,$G$6)</f>
-        <v>1450</v>
+        <f t="shared" si="2"/>
+        <v>1750</v>
       </c>
       <c r="K19" s="8">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L19" s="7"/>
       <c r="M19" s="9">
-        <f t="shared" si="2"/>
-        <v>1035300</v>
+        <f t="shared" si="4"/>
+        <v>1249500</v>
       </c>
       <c r="N19" s="9">
-        <f t="shared" si="3"/>
-        <v>1450</v>
+        <f t="shared" si="5"/>
+        <v>1750</v>
       </c>
       <c r="O19" s="6">
         <v>1</v>
       </c>
       <c r="P19" s="19" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="13" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C20" s="28" t="str">
         <f>'Hard Costs'!$B$31</f>
@@ -3870,7 +3883,7 @@
         <f>IF('Hard Costs'!$H$31=1,"Yes","No")</f>
         <v>No</v>
       </c>
-      <c r="G20" s="40">
+      <c r="G20" s="41">
         <v>858</v>
       </c>
       <c r="H20" s="33">
@@ -3882,34 +3895,35 @@
         <v>858</v>
       </c>
       <c r="J20" s="9">
-        <f>IF('Hard Costs'!$H$31=1,$G$8,$G$6)</f>
-        <v>1450</v>
+        <f t="shared" si="2"/>
+        <v>1750</v>
       </c>
       <c r="K20" s="8">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>0.02</v>
       </c>
       <c r="L20" s="7"/>
       <c r="M20" s="9">
-        <f t="shared" si="2"/>
-        <v>1244100</v>
+        <f t="shared" si="4"/>
+        <v>1531530</v>
       </c>
       <c r="N20" s="9">
-        <f t="shared" si="3"/>
-        <v>1450</v>
+        <f t="shared" si="5"/>
+        <v>1785</v>
       </c>
       <c r="O20" s="6">
         <v>1</v>
       </c>
       <c r="P20" s="19" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="21" spans="1:16" ht="13" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>135</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>133</v>
       </c>
       <c r="C21" s="28" t="str">
         <f>'Hard Costs'!$B$30</f>
@@ -3926,7 +3940,7 @@
         <f>IF('Hard Costs'!$H$30=1,"Yes","No")</f>
         <v>No</v>
       </c>
-      <c r="G21" s="40">
+      <c r="G21" s="41">
         <v>719</v>
       </c>
       <c r="H21" s="33">
@@ -3938,34 +3952,35 @@
         <v>719</v>
       </c>
       <c r="J21" s="9">
-        <f>IF('Hard Costs'!$H$30=1,$G$8,$G$6)</f>
-        <v>1450</v>
+        <f t="shared" si="2"/>
+        <v>1750</v>
       </c>
       <c r="K21" s="8">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>0.02</v>
       </c>
       <c r="L21" s="7"/>
       <c r="M21" s="9">
-        <f t="shared" si="2"/>
-        <v>1042550</v>
+        <f t="shared" si="4"/>
+        <v>1283415</v>
       </c>
       <c r="N21" s="9">
-        <f t="shared" si="3"/>
-        <v>1450</v>
+        <f t="shared" si="5"/>
+        <v>1785</v>
       </c>
       <c r="O21" s="6">
         <v>1</v>
       </c>
       <c r="P21" s="19" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="22" spans="1:16" ht="13" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C22" s="28" t="str">
         <f>'Hard Costs'!$B$31</f>
@@ -3982,7 +3997,7 @@
         <f>IF('Hard Costs'!$H$31=1,"Yes","No")</f>
         <v>No</v>
       </c>
-      <c r="G22" s="40">
+      <c r="G22" s="41">
         <v>858</v>
       </c>
       <c r="H22" s="33">
@@ -3994,34 +4009,35 @@
         <v>858</v>
       </c>
       <c r="J22" s="9">
-        <f>IF('Hard Costs'!$H$31=1,$G$8,$G$6)</f>
-        <v>1450</v>
+        <f t="shared" si="2"/>
+        <v>1750</v>
       </c>
       <c r="K22" s="8">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>0.04</v>
       </c>
       <c r="L22" s="7"/>
       <c r="M22" s="9">
-        <f t="shared" si="2"/>
-        <v>1244100</v>
+        <f t="shared" si="4"/>
+        <v>1561560</v>
       </c>
       <c r="N22" s="9">
-        <f t="shared" si="3"/>
-        <v>1450</v>
+        <f t="shared" si="5"/>
+        <v>1820</v>
       </c>
       <c r="O22" s="6">
         <v>1</v>
       </c>
       <c r="P22" s="19" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="13" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C23" s="28" t="str">
         <f>'Hard Costs'!$B$30</f>
@@ -4038,7 +4054,7 @@
         <f>IF('Hard Costs'!$H$30=1,"Yes","No")</f>
         <v>No</v>
       </c>
-      <c r="G23" s="40">
+      <c r="G23" s="41">
         <v>719</v>
       </c>
       <c r="H23" s="33">
@@ -4050,34 +4066,35 @@
         <v>719</v>
       </c>
       <c r="J23" s="9">
-        <f>IF('Hard Costs'!$H$30=1,$G$8,$G$6)</f>
-        <v>1450</v>
+        <f t="shared" si="2"/>
+        <v>1750</v>
       </c>
       <c r="K23" s="8">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>0.04</v>
       </c>
       <c r="L23" s="7"/>
       <c r="M23" s="9">
-        <f t="shared" si="2"/>
-        <v>1042550</v>
+        <f t="shared" si="4"/>
+        <v>1308580</v>
       </c>
       <c r="N23" s="9">
-        <f t="shared" si="3"/>
-        <v>1450</v>
+        <f t="shared" si="5"/>
+        <v>1820</v>
       </c>
       <c r="O23" s="6">
         <v>1</v>
       </c>
       <c r="P23" s="19" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="24" spans="1:16" ht="24" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C24" s="28" t="str">
         <f>'Hard Costs'!$B$32</f>
@@ -4094,7 +4111,7 @@
         <f>IF('Hard Costs'!$H$32=1,"Yes","No")</f>
         <v>No</v>
       </c>
-      <c r="G24" s="40">
+      <c r="G24" s="41">
         <v>567</v>
       </c>
       <c r="H24" s="33">
@@ -4106,34 +4123,35 @@
         <v>567</v>
       </c>
       <c r="J24" s="9">
-        <f>IF('Hard Costs'!$H$32=1,$G$8,$G$6)</f>
-        <v>1450</v>
+        <f t="shared" si="2"/>
+        <v>1750</v>
       </c>
       <c r="K24" s="8">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>0.06</v>
       </c>
       <c r="L24" s="7"/>
       <c r="M24" s="9">
-        <f t="shared" si="2"/>
-        <v>822150</v>
+        <f t="shared" si="4"/>
+        <v>1051785</v>
       </c>
       <c r="N24" s="9">
-        <f t="shared" si="3"/>
-        <v>1450</v>
+        <f t="shared" si="5"/>
+        <v>1855</v>
       </c>
       <c r="O24" s="6">
         <v>1</v>
       </c>
       <c r="P24" s="19" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="25" spans="1:16" ht="13" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="B25" s="4" t="s">
         <v>144</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>142</v>
       </c>
       <c r="C25" s="28" t="str">
         <f>'Hard Costs'!$B$30</f>
@@ -4150,7 +4168,7 @@
         <f>IF('Hard Costs'!$H$30=1,"Yes","No")</f>
         <v>No</v>
       </c>
-      <c r="G25" s="40">
+      <c r="G25" s="41">
         <v>723</v>
       </c>
       <c r="H25" s="33">
@@ -4162,34 +4180,35 @@
         <v>723</v>
       </c>
       <c r="J25" s="9">
-        <f>IF('Hard Costs'!$H$30=1,$G$8,$G$6)</f>
-        <v>1450</v>
+        <f t="shared" si="2"/>
+        <v>1750</v>
       </c>
       <c r="K25" s="8">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>0.06</v>
       </c>
       <c r="L25" s="7"/>
       <c r="M25" s="9">
-        <f t="shared" si="2"/>
-        <v>1048350</v>
+        <f t="shared" si="4"/>
+        <v>1341165</v>
       </c>
       <c r="N25" s="9">
-        <f t="shared" si="3"/>
-        <v>1450</v>
+        <f t="shared" si="5"/>
+        <v>1855</v>
       </c>
       <c r="O25" s="6">
         <v>1</v>
       </c>
       <c r="P25" s="19" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="26" spans="1:16" ht="24" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C26" s="28" t="str">
         <f>'Hard Costs'!$B$33</f>
@@ -4206,7 +4225,7 @@
         <f>IF('Hard Costs'!$H$33=1,"Yes","No")</f>
         <v>No</v>
       </c>
-      <c r="G26" s="40">
+      <c r="G26" s="41">
         <v>863</v>
       </c>
       <c r="H26" s="33">
@@ -4218,31 +4237,32 @@
         <v>863</v>
       </c>
       <c r="J26" s="9">
-        <f>IF('Hard Costs'!$H$33=1,$G$8,$G$6)</f>
-        <v>1450</v>
+        <f t="shared" si="2"/>
+        <v>1750</v>
       </c>
       <c r="K26" s="8">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>0.08</v>
       </c>
       <c r="L26" s="7"/>
       <c r="M26" s="9">
-        <f t="shared" si="2"/>
-        <v>1251350</v>
+        <f t="shared" si="4"/>
+        <v>1631070</v>
       </c>
       <c r="N26" s="9">
-        <f t="shared" si="3"/>
-        <v>1450</v>
+        <f t="shared" si="5"/>
+        <v>1890</v>
       </c>
       <c r="O26" s="6">
         <v>1</v>
       </c>
       <c r="P26" s="19" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="27" spans="1:16" ht="13" x14ac:dyDescent="0.3">
       <c r="A27" s="12" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B27" s="14"/>
       <c r="C27" s="14"/>
@@ -4272,11 +4292,11 @@
       <c r="L27" s="14"/>
       <c r="M27" s="13">
         <f>SUM(M18:M26)</f>
-        <v>9030450</v>
+        <v>11258605</v>
       </c>
       <c r="N27" s="13">
-        <f t="shared" si="3"/>
-        <v>1312.7562145660706</v>
+        <f t="shared" si="5"/>
+        <v>1636.6630324175026</v>
       </c>
       <c r="O27" s="10">
         <f>MAX(O18:O26)</f>
@@ -4286,161 +4306,161 @@
     </row>
     <row r="28" spans="1:16" ht="25" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G28" s="5" t="str">
         <f>IF(AND(COUNT(G18:G26)='Hard Costs'!$C$12,ABS(G27-$G$11)&lt;1),"OK","UNIT MIX CHANGED: update this list")</f>
         <v>OK</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="25" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M29" s="33">
         <f>IF(N(L18)&gt;0,0,H18*J18*(1+K18))+IF(N(L19)&gt;0,0,H19*J19*(1+K19))+IF(N(L20)&gt;0,0,H20*J20*(1+K20))+IF(N(L21)&gt;0,0,H21*J21*(1+K21))+IF(N(L22)&gt;0,0,H22*J22*(1+K22))+IF(N(L23)&gt;0,0,H23*J23*(1+K23))+IF(N(L24)&gt;0,0,H24*J24*(1+K24))+IF(N(L25)&gt;0,0,H25*J25*(1+K25))+IF(N(L26)&gt;0,0,H26*J26*(1+K26))</f>
         <v>0</v>
       </c>
       <c r="P29" s="19" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="31" spans="1:16" ht="13" x14ac:dyDescent="0.3">
       <c r="A31" s="18" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="32" spans="1:16" ht="13" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G32" s="42">
+      <c r="G32" s="43">
         <f>'Hard Costs'!$C$9</f>
         <v>1717</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G33" s="7">
         <v>65</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G34" s="42">
+      <c r="G34" s="43">
         <f>'Hard Costs'!$C$22</f>
         <v>2616</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="G35" s="41">
+        <v>162</v>
+      </c>
+      <c r="G35" s="42">
         <v>40</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G36" s="8">
         <v>0</v>
       </c>
       <c r="H36" s="4"/>
       <c r="I36" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="G37" s="8">
         <v>0.03</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="25" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="G38" s="28">
         <f>'Hard Costs'!$C$17</f>
         <v>1857</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G39" s="7">
         <v>25</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="G40" s="9">
         <f>($G$32*$G$33+$G$34*$G$35+$G$38*$G$39)*(1-$G$36-$G$37)</f>
         <v>254789.9</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G41" s="8">
         <v>0.05</v>
@@ -4456,39 +4476,39 @@
         <v>5095798</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="25" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="G43" s="9">
         <f>($G$32*$G$33+$G$34*$G$35+$G$38*$G$39)*(1-0.05-$G$37)/$G$41</f>
         <v>4833128</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="13" x14ac:dyDescent="0.3">
       <c r="A45" s="18" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G46" s="9">
         <f>$M$27</f>
-        <v>9030450</v>
+        <v>11258605</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
@@ -4500,7 +4520,7 @@
         <v>5095798</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="13" x14ac:dyDescent="0.3">
@@ -4509,20 +4529,20 @@
       </c>
       <c r="G48" s="13">
         <f>$G$46+$G$47</f>
-        <v>14126248</v>
+        <v>16354403</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="50" spans="1:16" ht="13" x14ac:dyDescent="0.3">
       <c r="A50" s="18" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="51" spans="1:16" ht="13" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
@@ -4530,24 +4550,24 @@
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="K51" s="3"/>
       <c r="L51" s="3"/>
       <c r="M51" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="N51" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="O51" s="3"/>
       <c r="P51" s="3" t="s">
@@ -4556,236 +4576,236 @@
     </row>
     <row r="52" spans="1:16" ht="13" x14ac:dyDescent="0.3">
       <c r="A52" s="18" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="53" spans="1:16" ht="25" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G53" s="9">
         <f>$M$27</f>
-        <v>9030450</v>
+        <v>11258605</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I53" s="8">
         <v>0.03</v>
       </c>
       <c r="J53" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="M53" s="9">
-        <f t="shared" ref="M53:M60" si="4">G53*I53</f>
-        <v>270913.5</v>
+        <f t="shared" ref="M53:M60" si="6">G53*I53</f>
+        <v>337758.14999999997</v>
       </c>
       <c r="N53" s="11">
-        <f t="shared" ref="N53:N61" si="5">M53/$G$48</f>
-        <v>1.9178022359511174E-2</v>
+        <f t="shared" ref="N53:N61" si="7">M53/$G$48</f>
+        <v>2.0652429195978598E-2</v>
       </c>
       <c r="P53" s="19" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="54" spans="1:16" ht="25" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="G54" s="9">
         <f>$M$27</f>
-        <v>9030450</v>
+        <v>11258605</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I54" s="25">
         <v>1.4250000000000001E-2</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="M54" s="9">
-        <f t="shared" si="4"/>
-        <v>128683.91250000001</v>
+        <f t="shared" si="6"/>
+        <v>160435.12125</v>
       </c>
       <c r="N54" s="11">
-        <f t="shared" si="5"/>
-        <v>9.1095606207678079E-3</v>
+        <f t="shared" si="7"/>
+        <v>9.8099038680898344E-3</v>
       </c>
       <c r="P54" s="19" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="55" spans="1:16" ht="25" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="G55" s="9">
         <f>$M$27</f>
-        <v>9030450</v>
+        <v>11258605</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I55" s="25">
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="M55" s="9">
-        <f t="shared" si="4"/>
-        <v>36121.800000000003</v>
+        <f t="shared" si="6"/>
+        <v>45034.42</v>
       </c>
       <c r="N55" s="11">
-        <f t="shared" si="5"/>
-        <v>2.5570696479348233E-3</v>
+        <f t="shared" si="7"/>
+        <v>2.7536572261304799E-3</v>
       </c>
       <c r="P55" s="19" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="G56" s="10">
         <f>'Hard Costs'!$C$12</f>
         <v>9</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="I56" s="7">
         <v>2500</v>
       </c>
       <c r="J56" s="4" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="M56" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>22500</v>
       </c>
       <c r="N56" s="11">
-        <f t="shared" si="5"/>
-        <v>1.592779625559455E-3</v>
+        <f t="shared" si="7"/>
+        <v>1.3757762970620206E-3</v>
       </c>
     </row>
     <row r="57" spans="1:16" ht="25" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G57" s="6">
         <v>1</v>
       </c>
       <c r="H57" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="I57" s="7">
         <v>25000</v>
       </c>
       <c r="J57" s="4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="M57" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>25000</v>
       </c>
       <c r="N57" s="11">
-        <f t="shared" si="5"/>
-        <v>1.7697551395105056E-3</v>
+        <f t="shared" si="7"/>
+        <v>1.5286403300689118E-3</v>
       </c>
     </row>
     <row r="58" spans="1:16" ht="25" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="G58" s="6">
         <v>1</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="I58" s="7">
         <v>35000</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="M58" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>35000</v>
       </c>
       <c r="N58" s="11">
-        <f t="shared" si="5"/>
-        <v>2.4776571953147078E-3</v>
+        <f t="shared" si="7"/>
+        <v>2.1400964620964763E-3</v>
       </c>
       <c r="P58" s="19" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G59" s="10">
         <f>'Hard Costs'!$H$34</f>
         <v>0</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="I59" s="7">
         <v>25000</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="M59" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="N59" s="11">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="P59" s="19" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="60" spans="1:16" ht="25" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="G60" s="9">
         <f>$M$27</f>
-        <v>9030450</v>
+        <v>11258605</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I60" s="8">
         <v>0</v>
       </c>
       <c r="J60" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="M60" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="N60" s="11">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="P60" s="19" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="61" spans="1:16" ht="13" x14ac:dyDescent="0.3">
       <c r="A61" s="12" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B61" s="14"/>
       <c r="C61" s="14"/>
@@ -4800,36 +4820,36 @@
       <c r="L61" s="14"/>
       <c r="M61" s="13">
         <f>SUM(M53:M60)</f>
-        <v>518219.21249999997</v>
+        <v>625727.69125000003</v>
       </c>
       <c r="N61" s="20">
-        <f t="shared" si="5"/>
-        <v>3.668484458859847E-2</v>
+        <f t="shared" si="7"/>
+        <v>3.8260503379426325E-2</v>
       </c>
       <c r="O61" s="14"/>
       <c r="P61" s="14"/>
     </row>
     <row r="63" spans="1:16" ht="13" x14ac:dyDescent="0.3">
       <c r="A63" s="18" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G64" s="9">
         <f>$G$42</f>
         <v>5095798</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I64" s="8">
         <v>0.06</v>
       </c>
       <c r="J64" s="4" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="M64" s="9">
         <f>G64*I64</f>
@@ -4837,25 +4857,25 @@
       </c>
       <c r="N64" s="11">
         <f>M64/$G$48</f>
-        <v>2.1643955280977654E-2</v>
+        <v>1.8695141608042802E-2</v>
       </c>
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="G65" s="9">
         <f>$G$42</f>
         <v>5095798</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I65" s="25">
         <v>2.6249999999999999E-2</v>
       </c>
       <c r="J65" s="4" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="M65" s="9">
         <f>G65*I65</f>
@@ -4863,28 +4883,28 @@
       </c>
       <c r="N65" s="11">
         <f>M65/$G$48</f>
-        <v>9.4692304354277237E-3</v>
+        <v>8.1791244535187255E-3</v>
       </c>
       <c r="P65" s="19" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="G66" s="9">
         <f>$G$42</f>
         <v>5095798</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I66" s="25">
         <v>6.4999999999999997E-3</v>
       </c>
       <c r="J66" s="4" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="M66" s="9">
         <f>G66*I66</f>
@@ -4892,28 +4912,28 @@
       </c>
       <c r="N66" s="11">
         <f>M66/$G$48</f>
-        <v>2.3447618221059123E-3</v>
+        <v>2.0253070075379699E-3</v>
       </c>
       <c r="P66" s="19" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="G67" s="9">
         <f>$G$42</f>
         <v>5095798</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I67" s="8">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="J67" s="4" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="M67" s="9">
         <f>G67*I67</f>
@@ -4921,12 +4941,12 @@
       </c>
       <c r="N67" s="11">
         <f>M67/$G$48</f>
-        <v>1.8036629400814711E-3</v>
+        <v>1.5579284673369002E-3</v>
       </c>
     </row>
     <row r="68" spans="1:16" ht="13" x14ac:dyDescent="0.3">
       <c r="A68" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B68" s="14"/>
       <c r="C68" s="14"/>
@@ -4945,31 +4965,31 @@
       </c>
       <c r="N68" s="20">
         <f>M68/$G$48</f>
-        <v>3.5261610478592754E-2</v>
+        <v>3.0457501536436393E-2</v>
       </c>
       <c r="O68" s="14"/>
       <c r="P68" s="14"/>
     </row>
     <row r="70" spans="1:16" ht="13" x14ac:dyDescent="0.3">
       <c r="A70" s="18" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="71" spans="1:16" ht="25" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="G71" s="6">
         <v>1</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="I71" s="7">
         <v>15000</v>
       </c>
       <c r="J71" s="4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="M71" s="9">
         <f>G71*I71</f>
@@ -4977,28 +4997,28 @@
       </c>
       <c r="N71" s="11">
         <f>M71/$G$48</f>
-        <v>1.0618530837063034E-3</v>
+        <v>9.1718419804134703E-4</v>
       </c>
       <c r="P71" s="19" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="72" spans="1:16" ht="25" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="G72" s="10">
         <f>'Hard Costs'!$C$12</f>
         <v>9</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="I72" s="7">
         <v>1000</v>
       </c>
       <c r="J72" s="4" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="M72" s="9">
         <f>G72*I72</f>
@@ -5006,27 +5026,27 @@
       </c>
       <c r="N72" s="11">
         <f>M72/$G$48</f>
-        <v>6.37111850223782E-4</v>
+        <v>5.5031051882480824E-4</v>
       </c>
       <c r="P72" s="19" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="73" spans="1:16" ht="25" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G73" s="6">
         <v>1</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="I73" s="7">
         <v>10000</v>
       </c>
       <c r="J73" s="4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="M73" s="9">
         <f>G73*I73</f>
@@ -5034,12 +5054,12 @@
       </c>
       <c r="N73" s="11">
         <f>M73/$G$48</f>
-        <v>7.0790205580420224E-4</v>
+        <v>6.1145613202756468E-4</v>
       </c>
     </row>
     <row r="74" spans="1:16" ht="13" x14ac:dyDescent="0.3">
       <c r="A74" s="12" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B74" s="14"/>
       <c r="C74" s="14"/>
@@ -5058,14 +5078,14 @@
       </c>
       <c r="N74" s="20">
         <f>M74/$G$48</f>
-        <v>2.4068669897342877E-3</v>
+        <v>2.0789508488937201E-3</v>
       </c>
       <c r="O74" s="14"/>
       <c r="P74" s="14"/>
     </row>
     <row r="76" spans="1:16" ht="13" x14ac:dyDescent="0.3">
       <c r="A76" s="15" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B76" s="15"/>
       <c r="C76" s="15"/>
@@ -5080,18 +5100,18 @@
       <c r="L76" s="15"/>
       <c r="M76" s="16">
         <f>M61+M68+M74</f>
-        <v>1050333.4669999999</v>
+        <v>1157841.94575</v>
       </c>
       <c r="N76" s="21">
         <f>M76/$G$48</f>
-        <v>7.4353322056925519E-2</v>
+        <v>7.0796955764756433E-2</v>
       </c>
       <c r="O76" s="15"/>
       <c r="P76" s="15"/>
     </row>
     <row r="78" spans="1:16" ht="13" x14ac:dyDescent="0.3">
       <c r="A78" s="15" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B78" s="15"/>
       <c r="C78" s="15"/>
@@ -5106,47 +5126,47 @@
       <c r="L78" s="15"/>
       <c r="M78" s="16">
         <f>$G$48-M76</f>
-        <v>13075914.533</v>
+        <v>15196561.05425</v>
       </c>
       <c r="N78" s="21">
         <f>M78/$G$48</f>
-        <v>0.92564667794307443</v>
+        <v>0.92920304423524358</v>
       </c>
       <c r="O78" s="15"/>
       <c r="P78" s="15"/>
     </row>
     <row r="79" spans="1:16" ht="13" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="81" spans="1:16" ht="13" x14ac:dyDescent="0.3">
       <c r="A81" s="18" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="M82" s="33">
         <f>$M$29*(1-$I$53-$I$54-$I$55-$I$60)</f>
         <v>0</v>
       </c>
       <c r="P82" s="19" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M83" s="33">
         <f>($G$42-$G$43)*(1-I64-I65-I66-I67)</f>
         <v>236994.00750000001</v>
       </c>
       <c r="P83" s="19" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -5172,196 +5192,196 @@
   <sheetData>
     <row r="1" spans="1:4" ht="18" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="13" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="13" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="13" x14ac:dyDescent="0.3">
       <c r="A5" s="18" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B6" s="6">
         <v>6</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B7" s="6">
         <v>20</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B8" s="6">
         <v>6</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="9" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B9" s="6">
         <v>1</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B10" s="10">
         <f>$B$6+$B$7+$B$8</f>
         <v>32</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A12" s="18" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B13" s="8">
         <v>0.7</v>
       </c>
       <c r="C13" s="4"/>
       <c r="D13" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B14" s="8">
         <v>9.5000000000000001E-2</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="37.5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B15" s="8">
         <v>0.01</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B16" s="8">
         <v>0.1</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A18" s="18" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B19" s="8">
         <v>0.08</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="25" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B20" s="8">
         <v>0.3</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B21" s="8">
         <v>0.1</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="13" outlineLevel="1" x14ac:dyDescent="0.3">
@@ -5372,30 +5392,30 @@
         <v>0</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A24" s="18" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B25" s="26">
         <f>'Soft Costs'!$C$7</f>
         <v>4000000</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="13" outlineLevel="1" x14ac:dyDescent="0.3">
@@ -5407,37 +5427,37 @@
         <v>0</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="27" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B27" s="26">
         <f>'Hard Costs'!$G$121</f>
         <v>6533100</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B28" s="26">
         <f>'Soft Costs'!$G$49</f>
         <v>1549116.8000000003</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="13" outlineLevel="1" x14ac:dyDescent="0.3">
@@ -5449,111 +5469,111 @@
         <v>260492.59420800002</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="30" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B30" s="26">
         <f>'Rev &amp; Unit-by-Unit'!$M$27</f>
-        <v>9030450</v>
+        <v>11258605</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B31" s="26">
         <f>'Rev &amp; Unit-by-Unit'!$M$61</f>
-        <v>518219.21249999997</v>
+        <v>625727.69125000003</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="32" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B32" s="26">
         <f>'Rev &amp; Unit-by-Unit'!$G$42</f>
         <v>5095798</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="33" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B33" s="26">
         <f>'Rev &amp; Unit-by-Unit'!$M$68</f>
         <v>498114.25449999998</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B34" s="26">
         <f>'Rev &amp; Unit-by-Unit'!$M$74+'Soft Costs'!$G$59</f>
         <v>96665.5</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A36" s="18" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B37" s="9">
         <f>$B$25+$B$26+$B$27+$B$28</f>
         <v>12082216.800000001</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B38" s="9">
         <f>$B$13*$B$37*(1+$B$16)</f>
         <v>9303306.9360000007</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="39" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -5565,37 +5585,37 @@
         <v>93033.069360000009</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B40" s="9">
         <f>$B$25+$B$26+$B$28*($B$6+1)/($B$6+$B$7+1)</f>
         <v>4401622.8740740744</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B41" s="9">
         <f>MAX((1-$B$13)*($B$37+$B$29),$B$40)</f>
         <v>4401622.8740740744</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="42" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -5607,51 +5627,51 @@
         <v>0</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B43" s="9">
         <f>$B$41+$B$42</f>
         <v>4401622.8740740744</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="13" x14ac:dyDescent="0.3">
       <c r="A45" s="18" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B46" s="9">
         <f>B78+B82</f>
         <v>13035860.548407018</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B47" s="9">
         <f>B82</f>
         <v>600118.08483901853</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="13" x14ac:dyDescent="0.3">
@@ -5663,25 +5683,25 @@
         <v>8634237.674332941</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="13" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B49" s="9">
         <f>$B$38-B48</f>
         <v>669069.26166705973</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -5693,19 +5713,19 @@
         <v>4401622.8740740744</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B51" s="9">
         <f>B90</f>
-        <v>13013249.033</v>
+        <v>15133895.55425</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="13" x14ac:dyDescent="0.3">
@@ -5714,13 +5734,13 @@
       </c>
       <c r="B52" s="9">
         <f>B99</f>
-        <v>-22611.51540701557</v>
+        <v>2098035.0058429847</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -5729,7 +5749,7 @@
       </c>
       <c r="B53" s="11">
         <f>B52/B46</f>
-        <v>-1.7345625417708765E-3</v>
+        <v>0.16094334532439936</v>
       </c>
       <c r="C53" s="4"/>
     </row>
@@ -5739,7 +5759,7 @@
       </c>
       <c r="B54" s="27">
         <f>B98/B81</f>
-        <v>0.99486291396289328</v>
+        <v>1.4766503323582276</v>
       </c>
       <c r="C54" s="4"/>
     </row>
@@ -5749,11 +5769,11 @@
       </c>
       <c r="B55" s="11">
         <f>B52/B50</f>
-        <v>-5.1370860371067403E-3</v>
+        <v>0.47665033235822762</v>
       </c>
       <c r="C55" s="4"/>
       <c r="D55" s="2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="13" x14ac:dyDescent="0.3">
@@ -5762,13 +5782,13 @@
       </c>
       <c r="B56" s="11">
         <f>IFERROR((1+IRR(D99:AY99))^12-1,"n/a")</f>
-        <v>-2.3193882013247125E-3</v>
+        <v>0.19175426332777623</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="13" x14ac:dyDescent="0.3">
@@ -5777,25 +5797,25 @@
       </c>
       <c r="B57" s="11">
         <f>IFERROR((1+IRR(D112:AY112))^12-1,"n/a")</f>
-        <v>5.9801144244321813E-2</v>
+        <v>0.18673943747403277</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B58" s="9">
         <f>B108</f>
-        <v>-20350.363866314568</v>
+        <v>1517900.7406042304</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -5804,7 +5824,7 @@
       </c>
       <c r="B59" s="27">
         <f>(B108+B81*(1-$B$21))/(B81*(1-$B$21))</f>
-        <v>0.99486291396289306</v>
+        <v>1.3831669424436841</v>
       </c>
       <c r="C59" s="4"/>
     </row>
@@ -5814,74 +5834,74 @@
       </c>
       <c r="B60" s="11">
         <f>IFERROR((1+IRR(D108:AY108))^12-1,"n/a")</f>
-        <v>-2.3193882013247125E-3</v>
+        <v>0.15722847952732177</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B61" s="9">
         <f>B106</f>
-        <v>0</v>
+        <v>411478.62739383924</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B62" s="9">
         <f>B109</f>
-        <v>-2261.1515407016977</v>
+        <v>580134.26523875375</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="13" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B63" s="11">
         <f>IFERROR((1+IRR(D109:AY109))^12-1,"n/a")</f>
-        <v>-2.3193882013247125E-3</v>
+        <v>0.45915342500232237</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B64" s="9">
         <f>AY95</f>
         <v>0</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="66" spans="1:51" ht="13" x14ac:dyDescent="0.3">
       <c r="A66" s="18" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="67" spans="1:51" ht="13" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C67" s="3"/>
       <c r="D67" s="29">
@@ -6031,7 +6051,7 @@
     </row>
     <row r="68" spans="1:51" ht="13" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D68" s="30" t="str">
         <f t="shared" ref="D68:AY68" si="0">IF(D$67=0,"Close",IF(D$67&lt;=$B$6,"Pre-dev",IF(D$67&lt;=$B$6+$B$7,"Build",IF(D$67&lt;=$B$10,"Sell",""))))</f>
@@ -6228,7 +6248,7 @@
     </row>
     <row r="70" spans="1:51" ht="13" x14ac:dyDescent="0.3">
       <c r="A70" s="18" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="71" spans="1:51" x14ac:dyDescent="0.25">
@@ -6434,7 +6454,7 @@
     </row>
     <row r="72" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B72" s="9">
         <f t="shared" si="1"/>
@@ -6635,7 +6655,7 @@
     </row>
     <row r="73" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B73" s="9">
         <f t="shared" si="1"/>
@@ -6836,7 +6856,7 @@
     </row>
     <row r="74" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B74" s="9">
         <f t="shared" si="1"/>
@@ -7037,7 +7057,7 @@
     </row>
     <row r="75" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B75" s="9">
         <f t="shared" si="1"/>
@@ -7640,7 +7660,7 @@
     </row>
     <row r="78" spans="1:51" ht="13" x14ac:dyDescent="0.3">
       <c r="A78" s="12" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B78" s="13">
         <f t="shared" si="1"/>
@@ -7841,12 +7861,12 @@
     </row>
     <row r="80" spans="1:51" ht="13" x14ac:dyDescent="0.3">
       <c r="A80" s="18" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="81" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B81" s="9">
         <f>SUM(D81:AY81)</f>
@@ -8047,7 +8067,7 @@
     </row>
     <row r="82" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B82" s="9">
         <f>SUM(D82:AY82)</f>
@@ -8248,7 +8268,7 @@
     </row>
     <row r="83" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B83" s="9">
         <f>SUM(D83:AY83)</f>
@@ -8449,16 +8469,16 @@
     </row>
     <row r="85" spans="1:51" ht="13" x14ac:dyDescent="0.3">
       <c r="A85" s="18" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="86" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B86" s="9">
         <f>SUM(D86:AY86)</f>
-        <v>9030450</v>
+        <v>11258605</v>
       </c>
       <c r="D86" s="9">
         <f>SUMPRODUCT(--('Rev &amp; Unit-by-Unit'!$O$18:$O$26+$B$6+$B$7=D$67),'Rev &amp; Unit-by-Unit'!$M$18:$M$26)</f>
@@ -8570,7 +8590,7 @@
       </c>
       <c r="AE86" s="9">
         <f>SUMPRODUCT(--('Rev &amp; Unit-by-Unit'!$O$18:$O$26+$B$6+$B$7=AE$67),'Rev &amp; Unit-by-Unit'!$M$18:$M$26)</f>
-        <v>9030450</v>
+        <v>11258605</v>
       </c>
       <c r="AF86" s="9">
         <f>SUMPRODUCT(--('Rev &amp; Unit-by-Unit'!$O$18:$O$26+$B$6+$B$7=AF$67),'Rev &amp; Unit-by-Unit'!$M$18:$M$26)</f>
@@ -8655,11 +8675,11 @@
     </row>
     <row r="87" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B87" s="9">
         <f>SUM(D87:AY87)</f>
-        <v>-518219.21250000002</v>
+        <v>-625727.69125000003</v>
       </c>
       <c r="D87" s="9">
         <f t="shared" ref="D87:AY87" si="11">-$B$31*D86/$B$30</f>
@@ -8771,7 +8791,7 @@
       </c>
       <c r="AE87" s="9">
         <f t="shared" si="11"/>
-        <v>-518219.21250000002</v>
+        <v>-625727.69125000003</v>
       </c>
       <c r="AF87" s="9">
         <f t="shared" si="11"/>
@@ -8856,7 +8876,7 @@
     </row>
     <row r="88" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B88" s="9">
         <f>SUM(D88:AY88)</f>
@@ -9057,7 +9077,7 @@
     </row>
     <row r="89" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B89" s="9">
         <f>SUM(D89:AY89)</f>
@@ -9258,11 +9278,11 @@
     </row>
     <row r="90" spans="1:51" ht="13" x14ac:dyDescent="0.3">
       <c r="A90" s="12" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B90" s="13">
         <f>SUM(D90:AY90)</f>
-        <v>13013249.033</v>
+        <v>15133895.55425</v>
       </c>
       <c r="D90" s="13">
         <f t="shared" ref="D90:AY90" si="14">SUM(D86:D89)</f>
@@ -9374,7 +9394,7 @@
       </c>
       <c r="AE90" s="13">
         <f t="shared" si="14"/>
-        <v>13109914.533</v>
+        <v>15230561.05425</v>
       </c>
       <c r="AF90" s="13">
         <f t="shared" si="14"/>
@@ -9459,12 +9479,12 @@
     </row>
     <row r="92" spans="1:51" ht="13" x14ac:dyDescent="0.3">
       <c r="A92" s="18" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="93" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D93" s="9">
         <f t="shared" ref="D93:AY93" si="15">N(C95)+D83</f>
@@ -9661,7 +9681,7 @@
     </row>
     <row r="94" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B94" s="9">
         <f>SUM(D94:AY94)</f>
@@ -9862,7 +9882,7 @@
     </row>
     <row r="95" spans="1:51" ht="13" x14ac:dyDescent="0.3">
       <c r="A95" s="12" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D95" s="13">
         <f t="shared" ref="D95:AY95" si="17">D93-D94</f>
@@ -10059,16 +10079,16 @@
     </row>
     <row r="97" spans="1:51" ht="13" x14ac:dyDescent="0.3">
       <c r="A97" s="18" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="98" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B98" s="9">
         <f>SUM(D98:AY98)</f>
-        <v>4379011.3586670589</v>
+        <v>6499657.8799170591</v>
       </c>
       <c r="D98" s="9">
         <f t="shared" ref="D98:AY98" si="18">D90-D94</f>
@@ -10180,7 +10200,7 @@
       </c>
       <c r="AE98" s="9">
         <f t="shared" si="18"/>
-        <v>4475676.8586670589</v>
+        <v>6596323.3799170591</v>
       </c>
       <c r="AF98" s="9">
         <f t="shared" si="18"/>
@@ -10265,11 +10285,11 @@
     </row>
     <row r="99" spans="1:51" ht="13" x14ac:dyDescent="0.3">
       <c r="A99" s="12" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B99" s="13">
         <f>SUM(D99:AY99)</f>
-        <v>-22611.51540701557</v>
+        <v>2098035.0058429847</v>
       </c>
       <c r="D99" s="13">
         <f t="shared" ref="D99:AY99" si="19">D98-D81</f>
@@ -10381,7 +10401,7 @@
       </c>
       <c r="AE99" s="13">
         <f t="shared" si="19"/>
-        <v>4475676.8586670589</v>
+        <v>6596323.3799170591</v>
       </c>
       <c r="AF99" s="13">
         <f t="shared" si="19"/>
@@ -10466,12 +10486,12 @@
     </row>
     <row r="101" spans="1:51" ht="13" x14ac:dyDescent="0.3">
       <c r="A101" s="18" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="102" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D102" s="9">
         <f t="shared" ref="D102:AY102" si="20">N(C104)*(1+$B$19)^(1/12)+D81</f>
@@ -10587,92 +10607,92 @@
       </c>
       <c r="AF102" s="9">
         <f t="shared" si="20"/>
-        <v>753870.51391334983</v>
+        <v>0</v>
       </c>
       <c r="AG102" s="9">
         <f t="shared" si="20"/>
-        <v>758720.93949891208</v>
+        <v>0</v>
       </c>
       <c r="AH102" s="9">
         <f t="shared" si="20"/>
-        <v>763602.57286873821</v>
+        <v>0</v>
       </c>
       <c r="AI102" s="9">
         <f t="shared" si="20"/>
-        <v>768515.61481465178</v>
+        <v>0</v>
       </c>
       <c r="AJ102" s="9">
         <f t="shared" si="20"/>
-        <v>773460.267420377</v>
+        <v>0</v>
       </c>
       <c r="AK102" s="9">
         <f t="shared" si="20"/>
-        <v>778436.73406985099</v>
+        <v>0</v>
       </c>
       <c r="AL102" s="9">
         <f t="shared" si="20"/>
-        <v>783445.21945558919</v>
+        <v>0</v>
       </c>
       <c r="AM102" s="9">
         <f t="shared" si="20"/>
-        <v>788485.92958710471</v>
+        <v>0</v>
       </c>
       <c r="AN102" s="9">
         <f t="shared" si="20"/>
-        <v>793559.07179938222</v>
+        <v>0</v>
       </c>
       <c r="AO102" s="9">
         <f t="shared" si="20"/>
-        <v>798664.85476140585</v>
+        <v>0</v>
       </c>
       <c r="AP102" s="9">
         <f t="shared" si="20"/>
-        <v>803803.48848474224</v>
+        <v>0</v>
       </c>
       <c r="AQ102" s="9">
         <f t="shared" si="20"/>
-        <v>808975.18433217891</v>
+        <v>0</v>
       </c>
       <c r="AR102" s="9">
         <f t="shared" si="20"/>
-        <v>814180.15502641769</v>
+        <v>0</v>
       </c>
       <c r="AS102" s="9">
         <f t="shared" si="20"/>
-        <v>819418.61465882487</v>
+        <v>0</v>
       </c>
       <c r="AT102" s="9">
         <f t="shared" si="20"/>
-        <v>824690.77869823703</v>
+        <v>0</v>
       </c>
       <c r="AU102" s="9">
         <f t="shared" si="20"/>
-        <v>829996.86399982369</v>
+        <v>0</v>
       </c>
       <c r="AV102" s="9">
         <f t="shared" si="20"/>
-        <v>835337.088814007</v>
+        <v>0</v>
       </c>
       <c r="AW102" s="9">
         <f t="shared" si="20"/>
-        <v>840711.67279543891</v>
+        <v>0</v>
       </c>
       <c r="AX102" s="9">
         <f t="shared" si="20"/>
-        <v>846120.83701203612</v>
+        <v>0</v>
       </c>
       <c r="AY102" s="9">
         <f t="shared" si="20"/>
-        <v>851564.80395407288</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B103" s="9">
         <f>SUM(D103:AY103)</f>
-        <v>4475676.8586670589</v>
+        <v>5224727.9552709283</v>
       </c>
       <c r="D103" s="9">
         <f t="shared" ref="D103:AY103" si="21">MIN(MAX(D98,0),D102)</f>
@@ -10784,7 +10804,7 @@
       </c>
       <c r="AE103" s="9">
         <f t="shared" si="21"/>
-        <v>4475676.8586670589</v>
+        <v>5224727.9552709283</v>
       </c>
       <c r="AF103" s="9">
         <f t="shared" si="21"/>
@@ -10869,7 +10889,7 @@
     </row>
     <row r="104" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D104" s="9">
         <f t="shared" ref="D104:AY104" si="22">D102-D103</f>
@@ -10981,96 +11001,96 @@
       </c>
       <c r="AE104" s="9">
         <f t="shared" si="22"/>
-        <v>749051.09660386946</v>
+        <v>0</v>
       </c>
       <c r="AF104" s="9">
         <f t="shared" si="22"/>
-        <v>753870.51391334983</v>
+        <v>0</v>
       </c>
       <c r="AG104" s="9">
         <f t="shared" si="22"/>
-        <v>758720.93949891208</v>
+        <v>0</v>
       </c>
       <c r="AH104" s="9">
         <f t="shared" si="22"/>
-        <v>763602.57286873821</v>
+        <v>0</v>
       </c>
       <c r="AI104" s="9">
         <f t="shared" si="22"/>
-        <v>768515.61481465178</v>
+        <v>0</v>
       </c>
       <c r="AJ104" s="9">
         <f t="shared" si="22"/>
-        <v>773460.267420377</v>
+        <v>0</v>
       </c>
       <c r="AK104" s="9">
         <f t="shared" si="22"/>
-        <v>778436.73406985099</v>
+        <v>0</v>
       </c>
       <c r="AL104" s="9">
         <f t="shared" si="22"/>
-        <v>783445.21945558919</v>
+        <v>0</v>
       </c>
       <c r="AM104" s="9">
         <f t="shared" si="22"/>
-        <v>788485.92958710471</v>
+        <v>0</v>
       </c>
       <c r="AN104" s="9">
         <f t="shared" si="22"/>
-        <v>793559.07179938222</v>
+        <v>0</v>
       </c>
       <c r="AO104" s="9">
         <f t="shared" si="22"/>
-        <v>798664.85476140585</v>
+        <v>0</v>
       </c>
       <c r="AP104" s="9">
         <f t="shared" si="22"/>
-        <v>803803.48848474224</v>
+        <v>0</v>
       </c>
       <c r="AQ104" s="9">
         <f t="shared" si="22"/>
-        <v>808975.18433217891</v>
+        <v>0</v>
       </c>
       <c r="AR104" s="9">
         <f t="shared" si="22"/>
-        <v>814180.15502641769</v>
+        <v>0</v>
       </c>
       <c r="AS104" s="9">
         <f t="shared" si="22"/>
-        <v>819418.61465882487</v>
+        <v>0</v>
       </c>
       <c r="AT104" s="9">
         <f t="shared" si="22"/>
-        <v>824690.77869823703</v>
+        <v>0</v>
       </c>
       <c r="AU104" s="9">
         <f t="shared" si="22"/>
-        <v>829996.86399982369</v>
+        <v>0</v>
       </c>
       <c r="AV104" s="9">
         <f t="shared" si="22"/>
-        <v>835337.088814007</v>
+        <v>0</v>
       </c>
       <c r="AW104" s="9">
         <f t="shared" si="22"/>
-        <v>840711.67279543891</v>
+        <v>0</v>
       </c>
       <c r="AX104" s="9">
         <f t="shared" si="22"/>
-        <v>846120.83701203612</v>
+        <v>0</v>
       </c>
       <c r="AY104" s="9">
         <f t="shared" si="22"/>
-        <v>851564.80395407288</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B105" s="9">
         <f>SUM(D105:AY105)</f>
-        <v>0</v>
+        <v>1371595.4246461308</v>
       </c>
       <c r="D105" s="9">
         <f t="shared" ref="D105:AY105" si="23">MAX(D98,0)-D103</f>
@@ -11182,7 +11202,7 @@
       </c>
       <c r="AE105" s="9">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>1371595.4246461308</v>
       </c>
       <c r="AF105" s="9">
         <f t="shared" si="23"/>
@@ -11271,7 +11291,7 @@
       </c>
       <c r="B106" s="9">
         <f>SUM(D106:AY106)</f>
-        <v>0</v>
+        <v>411478.62739383924</v>
       </c>
       <c r="D106" s="9">
         <f t="shared" ref="D106:AY106" si="24">D105*$B$20</f>
@@ -11383,7 +11403,7 @@
       </c>
       <c r="AE106" s="9">
         <f t="shared" si="24"/>
-        <v>0</v>
+        <v>411478.62739383924</v>
       </c>
       <c r="AF106" s="9">
         <f t="shared" si="24"/>
@@ -11468,11 +11488,11 @@
     </row>
     <row r="107" spans="1:51" ht="13" x14ac:dyDescent="0.3">
       <c r="A107" s="12" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B107" s="13">
         <f>SUM(D107:AY107)</f>
-        <v>-22611.51540701557</v>
+        <v>1686556.3784491457</v>
       </c>
       <c r="D107" s="13">
         <f t="shared" ref="D107:AY107" si="25">D103+D105-D106+MIN(D98,0)-D81</f>
@@ -11584,7 +11604,7 @@
       </c>
       <c r="AE107" s="13">
         <f t="shared" si="25"/>
-        <v>4475676.8586670589</v>
+        <v>6184844.7525232201</v>
       </c>
       <c r="AF107" s="13">
         <f t="shared" si="25"/>
@@ -11669,11 +11689,11 @@
     </row>
     <row r="108" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B108" s="9">
         <f>SUM(D108:AY108)</f>
-        <v>-20350.363866314568</v>
+        <v>1517900.7406042304</v>
       </c>
       <c r="D108" s="9">
         <f t="shared" ref="D108:AY108" si="26">D107*(1-$B$21)</f>
@@ -11785,7 +11805,7 @@
       </c>
       <c r="AE108" s="9">
         <f t="shared" si="26"/>
-        <v>4028109.1728003533</v>
+        <v>5566360.2772708982</v>
       </c>
       <c r="AF108" s="9">
         <f t="shared" si="26"/>
@@ -11870,11 +11890,11 @@
     </row>
     <row r="109" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B109" s="9">
         <f>SUM(D109:AY109)</f>
-        <v>-2261.1515407016977</v>
+        <v>580134.26523875375</v>
       </c>
       <c r="D109" s="9">
         <f t="shared" ref="D109:AY109" si="27">D107*$B$21+D106</f>
@@ -11986,7 +12006,7 @@
       </c>
       <c r="AE109" s="9">
         <f t="shared" si="27"/>
-        <v>447567.6858667059</v>
+        <v>1029963.1026461613</v>
       </c>
       <c r="AF109" s="9">
         <f t="shared" si="27"/>
@@ -12071,16 +12091,16 @@
     </row>
     <row r="111" spans="1:51" ht="13" x14ac:dyDescent="0.3">
       <c r="A111" s="18" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="112" spans="1:51" ht="13" x14ac:dyDescent="0.3">
       <c r="A112" s="12" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B112" s="13">
         <f>SUM(D112:AY112)</f>
-        <v>931032.23300000094</v>
+        <v>3051678.7542500012</v>
       </c>
       <c r="D112" s="13">
         <f t="shared" ref="D112:AY112" si="28">D90-D71-D72-D73-D74</f>
@@ -12192,7 +12212,7 @@
       </c>
       <c r="AE112" s="13">
         <f t="shared" si="28"/>
-        <v>13109914.533</v>
+        <v>15230561.05425</v>
       </c>
       <c r="AF112" s="13">
         <f t="shared" si="28"/>
@@ -12299,94 +12319,94 @@
   <sheetData>
     <row r="1" spans="1:59" ht="18" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="2" spans="1:59" ht="13" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3" spans="1:59" ht="13" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="5" spans="1:59" ht="13" x14ac:dyDescent="0.3">
       <c r="A5" s="18" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="6" spans="1:59" ht="13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B6" s="39">
         <v>46478</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="7" spans="1:59" ht="13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B7" s="28">
         <f>Finance!$B$6</f>
         <v>6</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="8" spans="1:59" ht="13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B8" s="28">
         <f>Finance!$B$7</f>
         <v>20</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="9" spans="1:59" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B9" s="28">
         <f>Finance!$B$8</f>
         <v>6</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10" spans="1:59" ht="25" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B10" s="6">
         <v>12</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="12" spans="1:59" ht="13" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -12557,16 +12577,16 @@
     </row>
     <row r="13" spans="1:59" ht="40" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="37">
@@ -12788,7 +12808,7 @@
     </row>
     <row r="14" spans="1:59" ht="13" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F14" s="30" t="str">
         <f t="shared" ref="F14:AK14" si="2">IF(F$12&lt;0,"Raise",IF(F$12=0,"Close",IF(F$12&lt;=$B$7,"Pre-dev",IF(F$12&lt;=$B$7+$B$8,"Build",IF(F$12&lt;=$B$7+$B$8+$B$9,"Sell","")))))</f>
@@ -13009,15 +13029,15 @@
     </row>
     <row r="16" spans="1:59" ht="13" x14ac:dyDescent="0.3">
       <c r="A16" s="18" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="17" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C17" s="6">
         <v>-6</v>
@@ -13244,7 +13264,7 @@
     </row>
     <row r="18" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C18" s="6">
         <v>-3</v>
@@ -13471,7 +13491,7 @@
     </row>
     <row r="19" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C19" s="6">
         <v>0</v>
@@ -13698,7 +13718,7 @@
     </row>
     <row r="20" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C20" s="6">
         <v>1</v>
@@ -13925,7 +13945,7 @@
     </row>
     <row r="21" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C21" s="6">
         <v>1</v>
@@ -14152,7 +14172,7 @@
     </row>
     <row r="22" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C22" s="6">
         <v>2</v>
@@ -14379,7 +14399,7 @@
     </row>
     <row r="23" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C23" s="6">
         <v>3</v>
@@ -14606,7 +14626,7 @@
     </row>
     <row r="24" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C24" s="6">
         <v>4</v>
@@ -14833,7 +14853,7 @@
     </row>
     <row r="25" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C25" s="6">
         <v>4</v>
@@ -15060,7 +15080,7 @@
     </row>
     <row r="26" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C26" s="6">
         <v>6</v>
@@ -15287,20 +15307,20 @@
     </row>
     <row r="28" spans="1:59" ht="13" x14ac:dyDescent="0.3">
       <c r="A28" s="18" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="29" spans="1:59" ht="13" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="30" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B30" s="26">
         <f>'Hard Costs'!$G$62</f>
@@ -15531,7 +15551,7 @@
     </row>
     <row r="31" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B31" s="26">
         <f>'Hard Costs'!$G$63</f>
@@ -15762,7 +15782,7 @@
     </row>
     <row r="32" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B32" s="26">
         <f>'Hard Costs'!$G$64</f>
@@ -15993,7 +16013,7 @@
     </row>
     <row r="33" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B33" s="26">
         <f>'Hard Costs'!$G$65</f>
@@ -16224,7 +16244,7 @@
     </row>
     <row r="34" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B34" s="26">
         <f>'Hard Costs'!$G$66</f>
@@ -16455,7 +16475,7 @@
     </row>
     <row r="35" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B35" s="26">
         <f>'Hard Costs'!$G$67</f>
@@ -16686,7 +16706,7 @@
     </row>
     <row r="36" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B36" s="26">
         <f>'Hard Costs'!$G$68</f>
@@ -16917,7 +16937,7 @@
     </row>
     <row r="37" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B37" s="26">
         <f>'Hard Costs'!$G$69</f>
@@ -17148,7 +17168,7 @@
     </row>
     <row r="38" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B38" s="26">
         <f>'Hard Costs'!$G$70</f>
@@ -17379,12 +17399,12 @@
     </row>
     <row r="39" spans="1:59" ht="13" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="40" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B40" s="26">
         <f>'Hard Costs'!$G$73</f>
@@ -17615,7 +17635,7 @@
     </row>
     <row r="41" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B41" s="26">
         <f>'Hard Costs'!$G$74</f>
@@ -17846,7 +17866,7 @@
     </row>
     <row r="42" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B42" s="26">
         <f>'Hard Costs'!$G$75</f>
@@ -18077,7 +18097,7 @@
     </row>
     <row r="43" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B43" s="26">
         <f>'Hard Costs'!$G$76</f>
@@ -18308,7 +18328,7 @@
     </row>
     <row r="44" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B44" s="26">
         <f>'Hard Costs'!$G$77</f>
@@ -18539,7 +18559,7 @@
     </row>
     <row r="45" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B45" s="26">
         <f>'Hard Costs'!$G$78</f>
@@ -18770,12 +18790,12 @@
     </row>
     <row r="46" spans="1:59" ht="13" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="47" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B47" s="26">
         <f>'Hard Costs'!$G$81</f>
@@ -19006,7 +19026,7 @@
     </row>
     <row r="48" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B48" s="26">
         <f>'Hard Costs'!$G$82</f>
@@ -19237,7 +19257,7 @@
     </row>
     <row r="49" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B49" s="26">
         <f>'Hard Costs'!$G$83</f>
@@ -19468,7 +19488,7 @@
     </row>
     <row r="50" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B50" s="26">
         <f>'Hard Costs'!$G$84</f>
@@ -19699,7 +19719,7 @@
     </row>
     <row r="51" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B51" s="26">
         <f>'Hard Costs'!$G$85</f>
@@ -19930,7 +19950,7 @@
     </row>
     <row r="52" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B52" s="26">
         <f>'Hard Costs'!$G$86</f>
@@ -20161,7 +20181,7 @@
     </row>
     <row r="53" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B53" s="26">
         <f>'Hard Costs'!$G$87</f>
@@ -20392,7 +20412,7 @@
     </row>
     <row r="54" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B54" s="26">
         <f>'Hard Costs'!$G$88</f>
@@ -20623,7 +20643,7 @@
     </row>
     <row r="55" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B55" s="26">
         <f>'Hard Costs'!$G$89</f>
@@ -20854,12 +20874,12 @@
     </row>
     <row r="56" spans="1:59" ht="13" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="57" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B57" s="26">
         <f>'Hard Costs'!$G$92</f>
@@ -21090,7 +21110,7 @@
     </row>
     <row r="58" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B58" s="26">
         <f>'Hard Costs'!$G$93</f>
@@ -21321,7 +21341,7 @@
     </row>
     <row r="59" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B59" s="26">
         <f>'Hard Costs'!$G$94</f>
@@ -21552,7 +21572,7 @@
     </row>
     <row r="60" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B60" s="26">
         <f>'Hard Costs'!$G$95</f>
@@ -21783,7 +21803,7 @@
     </row>
     <row r="61" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B61" s="26">
         <f>'Hard Costs'!$G$96</f>
@@ -22014,7 +22034,7 @@
     </row>
     <row r="62" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B62" s="26">
         <f>'Hard Costs'!$G$97</f>
@@ -22245,7 +22265,7 @@
     </row>
     <row r="63" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B63" s="26">
         <f>'Hard Costs'!$G$98</f>
@@ -22476,7 +22496,7 @@
     </row>
     <row r="64" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B64" s="26">
         <f>'Hard Costs'!$G$99</f>
@@ -22707,7 +22727,7 @@
     </row>
     <row r="65" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B65" s="26">
         <f>'Hard Costs'!$G$100</f>
@@ -22938,7 +22958,7 @@
     </row>
     <row r="66" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B66" s="26">
         <f>'Hard Costs'!$G$101</f>
@@ -23169,7 +23189,7 @@
     </row>
     <row r="67" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B67" s="26">
         <f>'Hard Costs'!$G$102</f>
@@ -23400,7 +23420,7 @@
     </row>
     <row r="68" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B68" s="26">
         <f>'Hard Costs'!$G$103</f>
@@ -23631,7 +23651,7 @@
     </row>
     <row r="69" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B69" s="26">
         <f>'Hard Costs'!$G$104</f>
@@ -23862,7 +23882,7 @@
     </row>
     <row r="70" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B70" s="26">
         <f>'Hard Costs'!$G$105</f>
@@ -24093,7 +24113,7 @@
     </row>
     <row r="71" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B71" s="26">
         <f>'Hard Costs'!$G$106</f>
@@ -24324,12 +24344,12 @@
     </row>
     <row r="72" spans="1:59" ht="13" x14ac:dyDescent="0.3">
       <c r="A72" s="5" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="73" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B73" s="26">
         <f>'Hard Costs'!$G$109</f>
@@ -24560,7 +24580,7 @@
     </row>
     <row r="74" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B74" s="26">
         <f>'Hard Costs'!$G$110</f>
@@ -24791,12 +24811,12 @@
     </row>
     <row r="75" spans="1:59" ht="13" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="76" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B76" s="26">
         <f>'Hard Costs'!$G$115</f>
@@ -25028,7 +25048,7 @@
     </row>
     <row r="77" spans="1:59" ht="13" x14ac:dyDescent="0.3">
       <c r="A77" s="12" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B77" s="13">
         <f>SUM(B29:B76)</f>
@@ -25256,7 +25276,7 @@
     </row>
     <row r="78" spans="1:59" ht="25" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B78" s="26">
         <f>'Hard Costs'!$G$121-B77</f>
@@ -25481,7 +25501,7 @@
     </row>
     <row r="79" spans="1:59" ht="13" x14ac:dyDescent="0.3">
       <c r="A79" s="15" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B79" s="16">
         <f>B77+B78</f>
@@ -25709,7 +25729,7 @@
     </row>
     <row r="80" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F80" s="35">
         <f>SUM($F$79:F79)</f>
@@ -25930,7 +25950,7 @@
     </row>
     <row r="81" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="F81" s="11" t="str">
         <f t="shared" ref="F81:AK81" si="42">IF(F79=0,"",F79/$B$79)</f>
@@ -26151,7 +26171,7 @@
     </row>
     <row r="82" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="F82" s="11" t="str">
         <f t="shared" ref="F82:AK82" si="44">IF(F12&lt;=$B$7,"",F80/$B$79)</f>
@@ -26372,7 +26392,7 @@
     </row>
     <row r="83" spans="1:59" ht="25" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B83" s="9">
         <f>SUM(F79:BG79)-'Hard Costs'!$G$121</f>
@@ -26381,15 +26401,15 @@
     </row>
     <row r="85" spans="1:59" ht="13" x14ac:dyDescent="0.3">
       <c r="A85" s="18" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="86" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C86" s="10">
         <f>$B$10</f>
@@ -26618,7 +26638,7 @@
     </row>
     <row r="87" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C87" s="10">
         <f>$B$7+$B$8+1</f>
@@ -26847,7 +26867,7 @@
     </row>
     <row r="88" spans="1:59" ht="13" x14ac:dyDescent="0.3">
       <c r="A88" s="4" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C88" s="10">
         <f>0</f>
@@ -27072,7 +27092,7 @@
     </row>
     <row r="89" spans="1:59" ht="13" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C89" s="10">
         <f>$B$7+1</f>
@@ -27297,7 +27317,7 @@
     </row>
     <row r="90" spans="1:59" ht="13" x14ac:dyDescent="0.3">
       <c r="A90" s="4" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C90" s="10">
         <f>$B$10</f>
@@ -27522,7 +27542,7 @@
     </row>
     <row r="91" spans="1:59" ht="13" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C91" s="10">
         <f>$B$7+$B$8</f>
@@ -27747,7 +27767,7 @@
     </row>
     <row r="92" spans="1:59" ht="13" x14ac:dyDescent="0.3">
       <c r="A92" s="4" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C92" s="10">
         <f>$B$7+$B$8+Finance!$B$9</f>
@@ -27972,7 +27992,7 @@
     </row>
     <row r="93" spans="1:59" ht="13" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C93" s="10">
         <f>$B$7+$B$8+$B$9</f>
@@ -28197,7 +28217,7 @@
     </row>
     <row r="94" spans="1:59" ht="13" x14ac:dyDescent="0.3">
       <c r="A94" s="4" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="F94" s="38" t="str">
         <f>IF(SUMPRODUCT(--('Rev &amp; Unit-by-Unit'!$O$18:$O$26+$B$7+$B$8=F$12))=0,"",SUMPRODUCT(--('Rev &amp; Unit-by-Unit'!$O$18:$O$26+$B$7+$B$8=F$12)))</f>
@@ -28418,7 +28438,7 @@
     </row>
     <row r="96" spans="1:59" ht="13" x14ac:dyDescent="0.3">
       <c r="A96" s="4" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B96" s="5" t="str">
         <f>IF('Rev &amp; Unit-by-Unit'!$O$27&lt;=$B$9,"OK","A unit closes after the sell-out period: extend it on Finance")</f>
@@ -28474,22 +28494,22 @@
   <sheetData>
     <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="13" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="13" x14ac:dyDescent="0.3">
       <c r="A5" s="18" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="6" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -28501,81 +28521,81 @@
         <v>14518</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="J6" s="19" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="7" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C7" s="6">
         <v>3060</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J7" s="19" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="8" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B8" s="4" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C8" s="6">
         <v>12</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="J8" s="19" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="24" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C9" s="6">
         <v>1717</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J9" s="19" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="10" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B10" s="4" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C10" s="10">
         <f>D34</f>
         <v>6879</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J10" s="19" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="24" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C11" s="6">
         <v>2855</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J11" s="19" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="12" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -28587,216 +28607,216 @@
         <v>9</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="J12" s="19" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="24" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B13" s="4" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C13" s="6">
         <v>1810</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="J13" s="19" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="24" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B14" s="4" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C14" s="6">
         <v>330</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="J14" s="19" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="36" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B15" s="4" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C15" s="6">
         <v>14518</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="J15" s="19" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="24" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B16" s="4" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C16" s="6">
         <v>5500</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J16" s="19" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="24" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B17" s="4" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C17" s="6">
         <v>1857</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J17" s="19" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="24" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B18" s="4" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C18" s="6">
         <v>8</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="J18" s="19" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="19" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B19" s="4" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C19" s="6">
         <v>78</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J19" s="19" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="24" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B20" s="4" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C20" s="8">
         <v>0.4</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="J20" s="19" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="24" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B21" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="C21" s="32">
+        <v>0</v>
+      </c>
+      <c r="D21" s="4" t="s">
         <v>480</v>
       </c>
-      <c r="C21" s="32">
-        <v>0</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>478</v>
-      </c>
       <c r="J21" s="19" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="22" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B22" s="4" t="s">
-        <v>482</v>
-      </c>
-      <c r="C22" s="43">
+        <v>484</v>
+      </c>
+      <c r="C22" s="44">
         <v>2616</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J22" s="19" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="24" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B23" s="4" t="s">
-        <v>484</v>
-      </c>
-      <c r="C23" s="44">
+        <v>486</v>
+      </c>
+      <c r="C23" s="45">
         <v>450</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="J23" s="19" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="24" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B24" s="4" t="s">
-        <v>487</v>
-      </c>
-      <c r="C24" s="45">
+        <v>489</v>
+      </c>
+      <c r="C24" s="46">
         <f>$C$6</f>
         <v>14518</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="J24" s="19" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="24" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B25" s="4" t="s">
-        <v>489</v>
-      </c>
-      <c r="C25" s="46">
+        <v>491</v>
+      </c>
+      <c r="C25" s="47">
         <v>1</v>
       </c>
       <c r="D25" s="4"/>
       <c r="J25" s="19" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="13" x14ac:dyDescent="0.3">
       <c r="A27" s="18" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="30" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B28" s="3" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="J28" s="3" t="s">
         <v>24</v>
@@ -28804,7 +28824,7 @@
     </row>
     <row r="29" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B29" s="4" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C29" s="6">
         <v>1</v>
@@ -28822,12 +28842,12 @@
         <v>1</v>
       </c>
       <c r="J29" s="19" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="30" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B30" s="4" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C30" s="6">
         <v>4</v>
@@ -28845,12 +28865,12 @@
         <v>1</v>
       </c>
       <c r="J30" s="19" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="31" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B31" s="4" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C31" s="6">
         <v>2</v>
@@ -28868,12 +28888,12 @@
         <v>2</v>
       </c>
       <c r="J31" s="19" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="32" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B32" s="4" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C32" s="6">
         <v>1</v>
@@ -28891,12 +28911,12 @@
         <v>1</v>
       </c>
       <c r="J32" s="19" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="24" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B33" s="4" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C33" s="6">
         <v>1</v>
@@ -28914,12 +28934,12 @@
         <v>2</v>
       </c>
       <c r="J33" s="19" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="24" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B34" s="12" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C34" s="10">
         <f>SUM(C29:C33)</f>
@@ -28945,184 +28965,184 @@
         <v>0</v>
       </c>
       <c r="J34" s="19" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="13" x14ac:dyDescent="0.3">
       <c r="A36" s="18" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="37" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B37" s="4" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C37" s="6">
         <v>3100</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J37" s="19" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="25" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B38" s="4" t="s">
-        <v>512</v>
-      </c>
-      <c r="C38" s="47">
+        <v>514</v>
+      </c>
+      <c r="C38" s="48">
         <v>4.8</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="J38" s="19" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="39" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B39" s="4" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C39" s="10">
         <f>C37*C38</f>
         <v>14880</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J39" s="19"/>
     </row>
     <row r="40" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B40" s="4" t="s">
-        <v>516</v>
-      </c>
-      <c r="C40" s="47">
+        <v>518</v>
+      </c>
+      <c r="C40" s="48">
         <v>2.2000000000000002</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="J40" s="19" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="41" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B41" s="4" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C41" s="10">
         <f>C37*C40</f>
         <v>6820.0000000000009</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J41" s="19"/>
     </row>
     <row r="42" spans="1:10" ht="24" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B42" s="4" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C42" s="6">
         <v>627</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J42" s="19" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="43" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B43" s="4" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C43" s="6">
         <v>6819</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J43" s="19" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="24" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B44" s="4" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C44" s="6">
         <v>858</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J44" s="19" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="45" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B45" s="4" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C45" s="6">
         <v>4234</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J45" s="19" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="46" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B46" s="4" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C46" s="10">
         <f>C37*2</f>
         <v>6200</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J46" s="19"/>
     </row>
     <row r="47" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B47" s="4" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C47" s="10">
         <f>C43+C44+C45</f>
         <v>11911</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J47" s="19" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="24" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B48" s="4" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C48" s="10">
         <f>C39-C47</f>
         <v>2969</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J48" s="19" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="49" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B49" s="4" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C49" s="10" t="str">
         <f>IF(C48&gt;=0,"PASS","OVER THE LIMIT")</f>
@@ -29133,7 +29153,7 @@
     </row>
     <row r="50" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B50" s="4" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C50" s="10" t="str">
         <f>IF(C43&lt;=C41+0.5,"PASS","OVER THE LIMIT")</f>
@@ -29141,12 +29161,12 @@
       </c>
       <c r="D50" s="4"/>
       <c r="J50" s="19" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="51" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B51" s="4" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C51" s="10" t="str">
         <f>IF(C45&lt;=C46,"PASS","OVER THE LIMIT")</f>
@@ -29157,35 +29177,35 @@
     </row>
     <row r="52" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B52" s="4" t="s">
-        <v>536</v>
-      </c>
-      <c r="C52" s="47">
+        <v>538</v>
+      </c>
+      <c r="C52" s="48">
         <v>84.92</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="J52" s="19" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="24" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B53" s="4" t="s">
-        <v>538</v>
-      </c>
-      <c r="C53" s="47">
+        <v>540</v>
+      </c>
+      <c r="C53" s="48">
         <v>85</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="J53" s="19" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="54" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B54" s="4" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C54" s="10" t="str">
         <f>IF(C52&lt;=C53,"PASS","TOO TALL")</f>
@@ -29219,31 +29239,31 @@
     </row>
     <row r="61" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="J61" s="3" t="s">
         <v>24</v>
@@ -29251,23 +29271,23 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C62" s="10">
         <f>$C$7*$C$8/27</f>
         <v>1360</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="E62" s="7">
         <v>45</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="G62" s="9">
         <f t="shared" ref="G62:G70" si="0">C62*E62</f>
@@ -29282,27 +29302,27 @@
         <v>9.3676814988290398E-3</v>
       </c>
       <c r="J62" s="19" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C63" s="6">
         <v>1</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E63" s="7">
         <v>70000</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="G63" s="9">
         <f t="shared" si="0"/>
@@ -29317,27 +29337,27 @@
         <v>1.0714668381013608E-2</v>
       </c>
       <c r="J63" s="19" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="64" spans="1:10" ht="24" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C64" s="6">
         <v>195</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="E64" s="7">
         <v>1200</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="G64" s="9">
         <f t="shared" si="0"/>
@@ -29352,27 +29372,27 @@
         <v>3.5817605730816916E-2</v>
       </c>
       <c r="J64" s="19" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C65" s="6">
         <v>299</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="E65" s="7">
         <v>340</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="G65" s="9">
         <f t="shared" si="0"/>
@@ -29387,22 +29407,22 @@
         <v>1.5560759823054906E-2</v>
       </c>
       <c r="J65" s="19" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C66" s="10">
         <f>$C$7</f>
         <v>3060</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E66" s="7">
         <v>18</v>
@@ -29426,16 +29446,16 @@
     </row>
     <row r="67" spans="1:10" ht="24" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C67" s="6">
         <v>0</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E67" s="7">
         <v>30</v>
@@ -29456,28 +29476,28 @@
         <v>0</v>
       </c>
       <c r="J67" s="19" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="24" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C68" s="10">
         <f>$C$13*$C$52/(10*$C$18+5)</f>
         <v>1808.2964705882355</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E68" s="7">
         <v>100</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="G68" s="9">
         <f t="shared" si="0"/>
@@ -29492,22 +29512,22 @@
         <v>2.7678995738443242E-2</v>
       </c>
       <c r="J68" s="19" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C69" s="10">
         <f>$C$6</f>
         <v>14518</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E69" s="7">
         <v>30</v>
@@ -29528,27 +29548,27 @@
         <v>6.6666666666666666E-2</v>
       </c>
       <c r="J69" s="19" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="24" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C70" s="6">
         <v>0</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="E70" s="7">
         <v>70</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="G70" s="9">
         <f t="shared" si="0"/>
@@ -29563,12 +29583,12 @@
         <v>0</v>
       </c>
       <c r="J70" s="19" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="71" spans="1:10" ht="13" x14ac:dyDescent="0.3">
       <c r="A71" s="12" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B71" s="14"/>
       <c r="C71" s="14"/>
@@ -29591,17 +29611,17 @@
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C73" s="10">
         <f>$C$16*$C$20</f>
         <v>2200</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="E73" s="7">
         <v>80</v>
@@ -29622,22 +29642,22 @@
         <v>2.6939737643691355E-2</v>
       </c>
       <c r="J73" s="19" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C74" s="10">
         <f>$C$16*(1-$C$20)</f>
         <v>3300</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="E74" s="7">
         <v>45</v>
@@ -29658,21 +29678,21 @@
         <v>2.2730403636864582E-2</v>
       </c>
       <c r="J74" s="19" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="75" spans="1:10" ht="24" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C75" s="6">
         <v>10670</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="E75" s="7">
         <v>42</v>
@@ -29693,27 +29713,27 @@
         <v>6.8595306975249112E-2</v>
       </c>
       <c r="J75" s="19" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C76" s="6">
         <v>0</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="E76" s="7">
         <v>320</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="G76" s="9">
         <f t="shared" si="3"/>
@@ -29731,16 +29751,16 @@
     </row>
     <row r="77" spans="1:10" ht="24" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C77" s="6">
         <v>5053</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E77" s="7">
         <v>38</v>
@@ -29761,27 +29781,27 @@
         <v>2.9390947635884956E-2</v>
       </c>
       <c r="J77" s="19" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C78" s="6">
         <v>1</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E78" s="7">
         <v>60000</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="G78" s="9">
         <f t="shared" si="3"/>
@@ -29796,12 +29816,12 @@
         <v>9.1840014694402356E-3</v>
       </c>
       <c r="J78" s="19" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="79" spans="1:10" ht="13" x14ac:dyDescent="0.3">
       <c r="A79" s="12" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B79" s="14"/>
       <c r="C79" s="14"/>
@@ -29824,23 +29844,23 @@
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C81" s="10">
         <f>$C$18+1</f>
         <v>9</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="E81" s="7">
         <v>55000</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="G81" s="9">
         <f t="shared" ref="G81:G89" si="6">C81*E81</f>
@@ -29855,28 +29875,28 @@
         <v>7.5768012122881936E-2</v>
       </c>
       <c r="J81" s="19" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C82" s="10">
         <f>C81</f>
         <v>9</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="E82" s="7">
         <v>22000</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="G82" s="9">
         <f t="shared" si="6"/>
@@ -29891,28 +29911,28 @@
         <v>3.0307204849152777E-2</v>
       </c>
       <c r="J82" s="19" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C83" s="10">
         <f>$C$12</f>
         <v>9</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E83" s="7">
         <v>30000</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G83" s="9">
         <f t="shared" si="6"/>
@@ -29927,28 +29947,28 @@
         <v>4.1328006612481059E-2</v>
       </c>
       <c r="J83" s="19" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C84" s="10">
         <f>$C$12</f>
         <v>9</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E84" s="7">
         <v>18000</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G84" s="9">
         <f t="shared" si="6"/>
@@ -29963,28 +29983,28 @@
         <v>2.4796803967488634E-2</v>
       </c>
       <c r="J84" s="19" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C85" s="10">
         <f>$C$12</f>
         <v>9</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E85" s="7">
         <v>6000</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G85" s="9">
         <f t="shared" si="6"/>
@@ -29999,28 +30019,28 @@
         <v>8.2656013224962112E-3</v>
       </c>
       <c r="J85" s="19" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C86" s="10">
         <f>$C$12</f>
         <v>9</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E86" s="7">
         <v>4000</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G86" s="9">
         <f t="shared" si="6"/>
@@ -30038,22 +30058,22 @@
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C87" s="6">
         <v>1</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E87" s="7">
         <v>75000</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="G87" s="9">
         <f t="shared" si="6"/>
@@ -30068,22 +30088,22 @@
         <v>1.1480001836800294E-2</v>
       </c>
       <c r="J87" s="19" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C88" s="10">
         <f>$C$9+$C$22</f>
         <v>4333</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E88" s="7">
         <v>28</v>
@@ -30104,28 +30124,28 @@
         <v>1.8570663237972785E-2</v>
       </c>
       <c r="J88" s="19" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C89" s="10">
         <f>$C$6+$C$7</f>
         <v>17578</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="E89" s="7">
         <v>14</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="G89" s="9">
         <f t="shared" si="6"/>
@@ -30140,12 +30160,12 @@
         <v>3.766848816029144E-2</v>
       </c>
       <c r="J89" s="19" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="90" spans="1:10" ht="13" x14ac:dyDescent="0.3">
       <c r="A90" s="12" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B90" s="14"/>
       <c r="C90" s="14"/>
@@ -30168,23 +30188,23 @@
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C92" s="10">
         <f>$C$14</f>
         <v>330</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="E92" s="7">
         <v>175</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="G92" s="9">
         <f t="shared" ref="G92:G106" si="9">C92*E92</f>
@@ -30199,28 +30219,28 @@
         <v>8.8396014143362258E-3</v>
       </c>
       <c r="J92" s="19" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C93" s="10">
         <f>$E$34</f>
         <v>495</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="E93" s="7">
         <v>110</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="G93" s="9">
         <f t="shared" si="9"/>
@@ -30235,28 +30255,28 @@
         <v>8.3344813335170138E-3</v>
       </c>
       <c r="J93" s="19" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C94" s="10">
         <f>$C$12</f>
         <v>9</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="E94" s="7">
         <v>2500</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="G94" s="9">
         <f t="shared" si="9"/>
@@ -30274,23 +30294,23 @@
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C95" s="10">
         <f>$F$34</f>
         <v>47</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="E95" s="7">
         <v>1200</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="G95" s="9">
         <f t="shared" si="9"/>
@@ -30305,22 +30325,22 @@
         <v>8.6329613812738213E-3</v>
       </c>
       <c r="J95" s="19" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C96" s="10">
         <f>$C$10</f>
         <v>6879</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="E96" s="7">
         <v>10</v>
@@ -30341,28 +30361,28 @@
         <v>1.052945768471323E-2</v>
       </c>
       <c r="J96" s="19" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C97" s="10">
         <f>$C$12</f>
         <v>9</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E97" s="7">
         <v>10000</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G97" s="9">
         <f t="shared" si="9"/>
@@ -30377,22 +30397,22 @@
         <v>1.3776002204160353E-2</v>
       </c>
       <c r="J97" s="19" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C98" s="10">
         <f>$C$10</f>
         <v>6879</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="E98" s="7">
         <v>30</v>
@@ -30416,23 +30436,23 @@
     </row>
     <row r="99" spans="1:10" ht="24" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C99" s="10">
         <f>$C$12</f>
         <v>9</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="E99" s="7">
         <v>18000</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="G99" s="9">
         <f t="shared" si="9"/>
@@ -30447,28 +30467,28 @@
         <v>2.4796803967488634E-2</v>
       </c>
       <c r="J99" s="19" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C100" s="10">
         <f>$C$12</f>
         <v>9</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="E100" s="7">
         <v>12000</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="G100" s="9">
         <f t="shared" si="9"/>
@@ -30483,28 +30503,28 @@
         <v>1.6531202644992422E-2</v>
       </c>
       <c r="J100" s="19" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C101" s="10">
         <f>$G$34</f>
         <v>12</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="E101" s="7">
         <v>14000</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="G101" s="9">
         <f t="shared" si="9"/>
@@ -30519,27 +30539,27 @@
         <v>2.571520411443266E-2</v>
       </c>
       <c r="J101" s="19" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C102" s="6">
         <v>1</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E102" s="7">
         <v>85000</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="G102" s="9">
         <f t="shared" si="9"/>
@@ -30554,22 +30574,22 @@
         <v>1.3010668748373666E-2</v>
       </c>
       <c r="J102" s="19" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C103" s="10">
         <f>$C$17</f>
         <v>1857</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E103" s="7">
         <v>60</v>
@@ -30590,27 +30610,27 @@
         <v>1.7054690728750516E-2</v>
       </c>
       <c r="J103" s="19" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C104" s="6">
         <v>1</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E104" s="7">
         <v>40000</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="G104" s="9">
         <f t="shared" si="9"/>
@@ -30625,22 +30645,22 @@
         <v>6.1226676462934901E-3</v>
       </c>
       <c r="J104" s="19" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C105" s="10">
         <f>$C$11</f>
         <v>2855</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E105" s="7">
         <v>85</v>
@@ -30664,16 +30684,16 @@
     </row>
     <row r="106" spans="1:10" ht="24" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C106" s="6">
         <v>5413</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E106" s="7">
         <v>75</v>
@@ -30694,12 +30714,12 @@
         <v>6.2141249942599994E-2</v>
       </c>
       <c r="J106" s="19" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="107" spans="1:10" ht="13" x14ac:dyDescent="0.3">
       <c r="A107" s="12" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B107" s="14"/>
       <c r="C107" s="14"/>
@@ -30722,22 +30742,22 @@
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C109" s="6">
         <v>25</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="E109" s="7">
         <v>850</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="G109" s="9">
         <f>C109*E109</f>
@@ -30752,27 +30772,27 @@
         <v>3.2526671870934166E-3</v>
       </c>
       <c r="J109" s="19" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="110" spans="1:10" ht="24" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C110" s="6">
         <v>0</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E110" s="7">
         <v>0</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="G110" s="9">
         <f>C110*E110</f>
@@ -30787,12 +30807,12 @@
         <v>0</v>
       </c>
       <c r="J110" s="19" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="111" spans="1:10" ht="13" x14ac:dyDescent="0.3">
       <c r="A111" s="12" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="B111" s="14"/>
       <c r="C111" s="14"/>
@@ -30815,7 +30835,7 @@
     </row>
     <row r="113" spans="1:10" ht="13" x14ac:dyDescent="0.3">
       <c r="A113" s="12" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B113" s="14"/>
       <c r="C113" s="14"/>
@@ -30838,23 +30858,23 @@
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" s="4" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C115" s="9">
         <f>G113</f>
         <v>5720959.6470588241</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="E115" s="8">
         <v>0.1</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="G115" s="9">
         <f>C115*E115</f>
@@ -30869,12 +30889,12 @@
         <v>8.7568836341994222E-2</v>
       </c>
       <c r="J115" s="19" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="116" spans="1:10" ht="13" x14ac:dyDescent="0.3">
       <c r="A116" s="12" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="B116" s="14"/>
       <c r="C116" s="14"/>
@@ -30897,23 +30917,23 @@
     </row>
     <row r="118" spans="1:10" ht="36" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C118" s="9">
         <f>G116</f>
         <v>6293055.6117647067</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="E118" s="8">
         <v>0.01</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="G118" s="9">
         <f>C118*E118</f>
@@ -30928,28 +30948,28 @@
         <v>9.6325719976193633E-3</v>
       </c>
       <c r="J118" s="19" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="C119" s="9">
         <f>G116+G118</f>
         <v>6355986.167882354</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="E119" s="8">
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="G119" s="9">
         <f>C119*E119</f>
@@ -30964,15 +30984,15 @@
         <v>7.2966732881966673E-2</v>
       </c>
       <c r="J119" s="19" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="120" spans="1:10" ht="24" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C120" s="9"/>
       <c r="D120" s="4"/>
@@ -30991,12 +31011,12 @@
         <v>-4.5856504641522529E-2</v>
       </c>
       <c r="J120" s="19" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="121" spans="1:10" ht="13" x14ac:dyDescent="0.3">
       <c r="A121" s="15" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B121" s="15"/>
       <c r="C121" s="15"/>
@@ -31019,15 +31039,15 @@
     </row>
     <row r="123" spans="1:10" ht="13" x14ac:dyDescent="0.3">
       <c r="A123" s="18" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B124" s="4" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="G124" s="9">
         <f>G121/$C$6</f>
@@ -31036,10 +31056,10 @@
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B125" s="4" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="G125" s="9">
         <f>G121/($C$6+$C$7)</f>
@@ -31048,7 +31068,7 @@
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B126" s="4" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="F126" s="4" t="s">
         <v>96</v>
@@ -31060,10 +31080,10 @@
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B127" s="4" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G127" s="9">
         <f>G121/$C$12</f>
@@ -31072,10 +31092,10 @@
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B128" s="4" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G128" s="9">
         <f>G116+G118+G119</f>
@@ -31085,10 +31105,10 @@
     <row r="129" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A129" s="2"/>
       <c r="B129" s="4" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="G129" s="9">
         <f>G128/$C$6</f>
@@ -31100,12 +31120,12 @@
     </row>
     <row r="131" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="132" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
   </sheetData>
@@ -31137,51 +31157,51 @@
   <sheetData>
     <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="13" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="13" x14ac:dyDescent="0.3">
       <c r="A5" s="18" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="24" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C6" s="26">
         <f>'Hard Costs'!$G$121</f>
         <v>6533100</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J6" s="19" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="7" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="C7" s="7">
         <v>4000000</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J7" s="19" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="8" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -31193,40 +31213,40 @@
         <v>14518</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="J8" s="19" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="9" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C9" s="28">
         <f>'Hard Costs'!$C$7</f>
         <v>3060</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J9" s="19" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="10" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B10" s="4" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="C10" s="10">
         <f>$C$8+$C$9</f>
         <v>17578</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="J10" s="19" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="11" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -31238,112 +31258,112 @@
         <v>9</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="J11" s="19" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="12" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B12" s="4" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C12" s="28">
         <f>Finance!$B$10</f>
         <v>32</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J12" s="19" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="36" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B13" s="4" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="C13" s="28">
         <f>Finance!$B$7</f>
         <v>20</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J13" s="19" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="24" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B14" s="4" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="C14" s="6">
         <v>36</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J14" s="19" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="24" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B15" s="4" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="C15" s="26">
         <f>Finance!$B$38</f>
         <v>9303306.9360000007</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J15" s="19" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="16" spans="1:10" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B16" s="4" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="C16" s="28">
         <v>0</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J16" s="19" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>24</v>
@@ -31351,7 +31371,7 @@
     </row>
     <row r="19" spans="1:10" ht="13" x14ac:dyDescent="0.3">
       <c r="A19" s="24" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="B19" s="24"/>
       <c r="C19" s="24"/>
@@ -31365,23 +31385,23 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="C20" s="9">
         <f>$C$7</f>
         <v>4000000</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="E20" s="8">
         <v>1</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="G20" s="9">
         <f>C20*E20</f>
@@ -31392,10 +31412,10 @@
         <v>0.61226676462934904</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="J20" s="19" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="13" x14ac:dyDescent="0.3">
@@ -31420,7 +31440,7 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>41</v>
@@ -31430,7 +31450,7 @@
         <v>0</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E23" s="7">
         <v>200</v>
@@ -31447,15 +31467,15 @@
         <v>0</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="J23" s="19" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="13" x14ac:dyDescent="0.3">
       <c r="A24" s="12" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B24" s="14"/>
       <c r="C24" s="14"/>
@@ -31475,7 +31495,7 @@
     </row>
     <row r="26" spans="1:10" ht="13" x14ac:dyDescent="0.3">
       <c r="A26" s="15" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="B26" s="15"/>
       <c r="C26" s="15"/>
@@ -31495,7 +31515,7 @@
     </row>
     <row r="28" spans="1:10" ht="13" x14ac:dyDescent="0.3">
       <c r="A28" s="24" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="B28" s="24"/>
       <c r="C28" s="24"/>
@@ -31509,22 +31529,22 @@
     </row>
     <row r="29" spans="1:10" ht="36" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="C29" s="6">
         <v>1</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E29" s="7">
         <v>300000</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="G29" s="9">
         <f t="shared" ref="G29:G35" si="0">C29*E29</f>
@@ -31535,30 +31555,30 @@
         <v>4.5920007347201176E-2</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="J29" s="19" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="C30" s="6">
         <v>1</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E30" s="7">
         <v>40000</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="G30" s="9">
         <f t="shared" si="0"/>
@@ -31569,30 +31589,30 @@
         <v>6.1226676462934901E-3</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="J30" s="19" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="C31" s="6">
         <v>1</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E31" s="7">
         <v>45000</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="G31" s="9">
         <f t="shared" si="0"/>
@@ -31603,31 +31623,31 @@
         <v>6.8880011020801763E-3</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="J31" s="19" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="C32" s="10">
         <f>$C$10</f>
         <v>17578</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="E32" s="17">
         <v>3.5</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="G32" s="9">
         <f t="shared" si="0"/>
@@ -31638,28 +31658,28 @@
         <v>9.41712204007286E-3</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="J32" s="19"/>
     </row>
     <row r="33" spans="1:10" ht="24" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="C33" s="6">
         <v>1</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E33" s="7">
         <v>5000</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="G33" s="9">
         <f t="shared" si="0"/>
@@ -31670,30 +31690,30 @@
         <v>7.6533345578668626E-4</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="J33" s="19" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="25" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="C34" s="6">
         <v>1</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E34" s="7">
         <v>0</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="G34" s="9">
         <f t="shared" si="0"/>
@@ -31704,30 +31724,30 @@
         <v>0</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="J34" s="19" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="25" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="C35" s="6">
         <v>1</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E35" s="7">
         <v>30000</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="G35" s="9">
         <f t="shared" si="0"/>
@@ -31738,31 +31758,31 @@
         <v>4.5920007347201178E-3</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="J35" s="19" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="24" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="C36" s="10">
         <f>$C$13</f>
         <v>20</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E36" s="7">
         <v>50000</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="G36" s="9">
         <f>C36*E36/12</f>
@@ -31773,31 +31793,31 @@
         <v>1.2755557596444771E-2</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="J36" s="19" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="36" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="C37" s="10">
         <f>$C$13</f>
         <v>20</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E37" s="7">
         <v>150000</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="G37" s="9">
         <f>C37*E37/12</f>
@@ -31808,31 +31828,31 @@
         <v>3.8266672789334315E-2</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="J37" s="19" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="24" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="C38" s="10">
         <f>$C$12-$C$13</f>
         <v>12</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E38" s="7">
         <v>30000</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="G38" s="9">
         <f>C38*E38/12</f>
@@ -31843,31 +31863,31 @@
         <v>4.5920007347201178E-3</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="J38" s="19" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="24" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="C39" s="10">
         <f>$C$14</f>
         <v>36</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E39" s="7">
         <v>67000</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="G39" s="9">
         <f>C39*E39/12</f>
@@ -31878,30 +31898,30 @@
         <v>3.0766404922624786E-2</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="J39" s="19" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="C40" s="6">
         <v>1</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E40" s="7">
         <v>10000</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="G40" s="9">
         <f t="shared" ref="G40:G45" si="2">C40*E40</f>
@@ -31912,30 +31932,30 @@
         <v>1.5306669115733725E-3</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="J40" s="19" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="24" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="C41" s="6">
         <v>1</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E41" s="7">
         <v>60000</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="G41" s="9">
         <f t="shared" si="2"/>
@@ -31946,30 +31966,30 @@
         <v>9.1840014694402356E-3</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="J41" s="19" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="C42" s="6">
         <v>1</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E42" s="7">
         <v>10000</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="G42" s="9">
         <f t="shared" si="2"/>
@@ -31980,31 +32000,31 @@
         <v>1.5306669115733725E-3</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="J42" s="19" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="C43" s="9">
         <f>$C$6</f>
         <v>6533100</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="E43" s="8">
         <v>0.03</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="G43" s="9">
         <f t="shared" si="2"/>
@@ -32015,31 +32035,31 @@
         <v>0.03</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="J43" s="19" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="C44" s="10">
         <f>$C$11</f>
         <v>9</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E44" s="7">
         <v>6500</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G44" s="9">
         <f t="shared" si="2"/>
@@ -32050,28 +32070,28 @@
         <v>8.9544014327042291E-3</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="J44" s="19"/>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="C45" s="6">
         <v>1</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E45" s="7">
         <v>95000</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="G45" s="9">
         <f t="shared" si="2"/>
@@ -32082,15 +32102,15 @@
         <v>1.4541335659947039E-2</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="J45" s="19" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="13" x14ac:dyDescent="0.3">
       <c r="A46" s="12" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="B46" s="14"/>
       <c r="C46" s="14"/>
@@ -32110,23 +32130,23 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="C48" s="9">
         <f>G46</f>
         <v>1475349.3333333335</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="E48" s="8">
         <v>0.05</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="G48" s="9">
         <f>C48*E48</f>
@@ -32137,13 +32157,13 @@
         <v>1.1291342037725839E-2</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="J48" s="19"/>
     </row>
     <row r="49" spans="1:10" ht="13" x14ac:dyDescent="0.3">
       <c r="A49" s="12" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="B49" s="14"/>
       <c r="C49" s="14"/>
@@ -32163,7 +32183,7 @@
     </row>
     <row r="51" spans="1:10" ht="24" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>47</v>
@@ -32173,13 +32193,13 @@
         <v>9303306.9360000007</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="E51" s="25">
         <v>2.8000000000000001E-2</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="G51" s="9">
         <f>C51*E51</f>
@@ -32190,15 +32210,15 @@
         <v>3.9872739466409519E-2</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="J51" s="19" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="13" x14ac:dyDescent="0.3">
       <c r="A52" s="15" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="B52" s="15"/>
       <c r="C52" s="15"/>
@@ -32218,7 +32238,7 @@
     </row>
     <row r="54" spans="1:10" ht="13" x14ac:dyDescent="0.3">
       <c r="A54" s="24" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="B54" s="24"/>
       <c r="C54" s="24"/>
@@ -32232,22 +32252,22 @@
     </row>
     <row r="55" spans="1:10" ht="25" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="C55" s="6">
         <v>1</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E55" s="7">
         <v>15000</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="G55" s="9">
         <f>C55*E55</f>
@@ -32258,29 +32278,29 @@
         <v>2.2960003673600589E-3</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="J55" s="19"/>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="C56" s="9">
         <f>$C$6</f>
         <v>6533100</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="E56" s="8">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="G56" s="9">
         <f>C56*E56</f>
@@ -32291,30 +32311,30 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="J56" s="19" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="C57" s="6">
         <v>1</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E57" s="7">
         <v>10000</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="G57" s="9">
         <f>C57*E57</f>
@@ -32325,28 +32345,28 @@
         <v>1.5306669115733725E-3</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="J57" s="19"/>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="C58" s="6">
         <v>1</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E58" s="7">
         <v>5000</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="G58" s="9">
         <f>C58*E58</f>
@@ -32357,13 +32377,13 @@
         <v>7.6533345578668626E-4</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="J58" s="19"/>
     </row>
     <row r="59" spans="1:10" ht="13" x14ac:dyDescent="0.3">
       <c r="A59" s="12" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="B59" s="14"/>
       <c r="C59" s="14"/>
@@ -32383,7 +32403,7 @@
     </row>
     <row r="61" spans="1:10" ht="13" x14ac:dyDescent="0.3">
       <c r="A61" s="15" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="B61" s="15"/>
       <c r="C61" s="15"/>
@@ -32403,12 +32423,12 @@
     </row>
     <row r="63" spans="1:10" ht="13" x14ac:dyDescent="0.3">
       <c r="A63" s="18" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B64" s="4" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="F64" s="4"/>
       <c r="G64" s="11">
@@ -32418,10 +32438,10 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B65" s="4" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G65" s="9">
         <f>G52/$C$11</f>
@@ -32430,12 +32450,12 @@
     </row>
     <row r="67" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="13" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
     </row>
   </sheetData>
